--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -6557,10 +6557,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119599641</v>
+        <v>119605869</v>
       </c>
       <c r="B54" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6573,39 +6573,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490793</v>
+        <v>490678</v>
       </c>
       <c r="R54" t="n">
-        <v>6943720</v>
+        <v>6943630</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6637,7 +6632,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6647,7 +6642,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6674,10 +6669,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119605869</v>
+        <v>119599504</v>
       </c>
       <c r="B55" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6690,21 +6685,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6714,10 +6709,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490678</v>
+        <v>490789</v>
       </c>
       <c r="R55" t="n">
-        <v>6943630</v>
+        <v>6943691</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6749,7 +6744,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6759,7 +6754,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6786,10 +6781,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119599504</v>
+        <v>119599641</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6802,34 +6797,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490789</v>
+        <v>490793</v>
       </c>
       <c r="R56" t="n">
-        <v>6943691</v>
+        <v>6943720</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6898,10 +6898,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119602140</v>
+        <v>119603940</v>
       </c>
       <c r="B57" t="n">
-        <v>82305</v>
+        <v>79643</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6910,25 +6910,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490645</v>
+        <v>490609</v>
       </c>
       <c r="R57" t="n">
-        <v>6943768</v>
+        <v>6943769</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7010,10 +7010,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119603940</v>
+        <v>119602140</v>
       </c>
       <c r="B58" t="n">
-        <v>79643</v>
+        <v>82305</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7022,25 +7022,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490609</v>
+        <v>490645</v>
       </c>
       <c r="R58" t="n">
-        <v>6943769</v>
+        <v>6943768</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -5338,10 +5338,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119611950</v>
+        <v>119611969</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5350,37 +5350,29 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5390,10 +5382,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490710</v>
+        <v>490646</v>
       </c>
       <c r="R43" t="n">
-        <v>6943807</v>
+        <v>6943773</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5453,10 +5445,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119611969</v>
+        <v>119611950</v>
       </c>
       <c r="B44" t="n">
-        <v>95455</v>
+        <v>97907</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5465,29 +5457,37 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490646</v>
+        <v>490710</v>
       </c>
       <c r="R44" t="n">
-        <v>6943773</v>
+        <v>6943807</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119569440</v>
+        <v>119564989</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490493</v>
+        <v>490648</v>
       </c>
       <c r="R3" t="n">
-        <v>6943708</v>
+        <v>6943345</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Många mycket gamla granar längs stranden</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119565471</v>
+        <v>119568892</v>
       </c>
       <c r="B4" t="n">
-        <v>74638</v>
+        <v>79607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,34 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490635</v>
+        <v>490488</v>
       </c>
       <c r="R4" t="n">
-        <v>6943355</v>
+        <v>6943660</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -983,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Många mycket gamla granar längs sjön</t>
+          <t>På stor asp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119570777</v>
+        <v>119569122</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,38 +1033,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490693</v>
+        <v>490488</v>
       </c>
       <c r="R5" t="n">
-        <v>6943819</v>
+        <v>6943685</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1100,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119569970</v>
+        <v>119568632</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,38 +1154,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490505</v>
+        <v>490519</v>
       </c>
       <c r="R6" t="n">
-        <v>6943750</v>
+        <v>6943605</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1212,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119566592</v>
+        <v>119568960</v>
       </c>
       <c r="B7" t="n">
-        <v>74638</v>
+        <v>79643</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,38 +1275,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490606</v>
+        <v>490488</v>
       </c>
       <c r="R7" t="n">
-        <v>6943414</v>
+        <v>6943660</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1324,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119568632</v>
+        <v>119570068</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,47 +1387,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490519</v>
+        <v>490537</v>
       </c>
       <c r="R8" t="n">
-        <v>6943605</v>
+        <v>6943742</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1445,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119563399</v>
+        <v>119567326</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>79635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,47 +1499,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490675</v>
+        <v>490636</v>
       </c>
       <c r="R9" t="n">
-        <v>6943404</v>
+        <v>6943499</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1566,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,7 +1599,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119570160</v>
+        <v>119567682</v>
       </c>
       <c r="B10" t="n">
         <v>79607</v>
@@ -1639,14 +1635,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490561</v>
+        <v>490645</v>
       </c>
       <c r="R10" t="n">
-        <v>6943765</v>
+        <v>6943575</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1678,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1684,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Vid surhål /kallkälla</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119562305</v>
+        <v>119569847</v>
       </c>
       <c r="B11" t="n">
-        <v>79115</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,38 +1728,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490757</v>
+        <v>490462</v>
       </c>
       <c r="R11" t="n">
-        <v>6943439</v>
+        <v>6943718</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1790,7 +1800,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1810,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119569122</v>
+        <v>119560369</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,50 +1849,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490488</v>
+        <v>490931</v>
       </c>
       <c r="R12" t="n">
-        <v>6943685</v>
+        <v>6943570</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1911,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1921,7 +1922,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,10 +1949,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119573937</v>
+        <v>119570901</v>
       </c>
       <c r="B13" t="n">
-        <v>90576</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,40 +1965,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490506</v>
+        <v>490713</v>
       </c>
       <c r="R13" t="n">
-        <v>6943700</v>
+        <v>6943822</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2024,18 +2022,27 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2054,10 +2061,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119569847</v>
+        <v>119569970</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,47 +2073,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490462</v>
+        <v>490505</v>
       </c>
       <c r="R14" t="n">
-        <v>6943718</v>
+        <v>6943750</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2138,7 +2136,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,7 +2146,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,10 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119562658</v>
+        <v>119565471</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,34 +2189,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490654</v>
+        <v>490635</v>
       </c>
       <c r="R15" t="n">
-        <v>6943443</v>
+        <v>6943355</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2250,7 +2248,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2258,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Många mycket gamla granar längs sjön</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,10 +2290,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119561375</v>
+        <v>119566746</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,34 +2306,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490834</v>
+        <v>490599</v>
       </c>
       <c r="R16" t="n">
-        <v>6943520</v>
+        <v>6943415</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2362,7 +2365,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2375,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2402,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119567978</v>
+        <v>119567943</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,21 +2418,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2439,10 +2442,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490638</v>
+        <v>490651</v>
       </c>
       <c r="R17" t="n">
-        <v>6943600</v>
+        <v>6943582</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2474,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2514,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119567265</v>
+        <v>119562305</v>
       </c>
       <c r="B18" t="n">
-        <v>79636</v>
+        <v>79115</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,25 +2526,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2551,10 +2554,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490622</v>
+        <v>490757</v>
       </c>
       <c r="R18" t="n">
-        <v>6943503</v>
+        <v>6943439</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2586,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,10 +2626,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119568797</v>
+        <v>119565821</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>74638</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2635,47 +2638,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490501</v>
+        <v>490631</v>
       </c>
       <c r="R19" t="n">
-        <v>6943638</v>
+        <v>6943382</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2707,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2717,7 +2711,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119561285</v>
+        <v>119569440</v>
       </c>
       <c r="B20" t="n">
-        <v>90558</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2756,38 +2750,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490846</v>
+        <v>490493</v>
       </c>
       <c r="R20" t="n">
-        <v>6943525</v>
+        <v>6943708</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2819,7 +2822,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2829,7 +2832,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2856,7 +2859,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119570334</v>
+        <v>119565707</v>
       </c>
       <c r="B21" t="n">
         <v>78526</v>
@@ -2892,14 +2895,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490582</v>
+        <v>490616</v>
       </c>
       <c r="R21" t="n">
-        <v>6943798</v>
+        <v>6943373</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2931,7 +2934,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2941,7 +2944,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2968,7 +2971,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119570068</v>
+        <v>119570160</v>
       </c>
       <c r="B22" t="n">
         <v>79607</v>
@@ -3008,10 +3011,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490537</v>
+        <v>490561</v>
       </c>
       <c r="R22" t="n">
-        <v>6943742</v>
+        <v>6943765</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3043,7 +3046,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3053,7 +3056,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3080,10 +3083,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119565707</v>
+        <v>119567047</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3096,34 +3099,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490616</v>
+        <v>490615</v>
       </c>
       <c r="R23" t="n">
-        <v>6943373</v>
+        <v>6943448</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3155,7 +3158,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3165,7 +3168,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3192,10 +3195,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119567047</v>
+        <v>119563399</v>
       </c>
       <c r="B24" t="n">
-        <v>74638</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,38 +3207,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490615</v>
+        <v>490675</v>
       </c>
       <c r="R24" t="n">
-        <v>6943448</v>
+        <v>6943404</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3267,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3277,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3304,10 +3316,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119567326</v>
+        <v>119560972</v>
       </c>
       <c r="B25" t="n">
-        <v>79635</v>
+        <v>90576</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3316,25 +3328,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3344,10 +3356,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490636</v>
+        <v>490865</v>
       </c>
       <c r="R25" t="n">
-        <v>6943499</v>
+        <v>6943527</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3379,7 +3391,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3389,7 +3401,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3416,10 +3428,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119570243</v>
+        <v>119566592</v>
       </c>
       <c r="B26" t="n">
-        <v>79607</v>
+        <v>74638</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3432,34 +3444,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490559</v>
+        <v>490606</v>
       </c>
       <c r="R26" t="n">
-        <v>6943786</v>
+        <v>6943414</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3491,7 +3503,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3501,7 +3513,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3528,7 +3540,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119570901</v>
+        <v>119562658</v>
       </c>
       <c r="B27" t="n">
         <v>78526</v>
@@ -3568,10 +3580,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490713</v>
+        <v>490654</v>
       </c>
       <c r="R27" t="n">
-        <v>6943822</v>
+        <v>6943443</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3603,7 +3615,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3613,7 +3625,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3640,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119565821</v>
+        <v>119567978</v>
       </c>
       <c r="B28" t="n">
-        <v>74638</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3656,34 +3668,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490631</v>
+        <v>490638</v>
       </c>
       <c r="R28" t="n">
-        <v>6943382</v>
+        <v>6943600</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3715,7 +3727,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3737,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3752,7 +3764,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119568892</v>
+        <v>119570243</v>
       </c>
       <c r="B29" t="n">
         <v>79607</v>
@@ -3788,14 +3800,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490488</v>
+        <v>490559</v>
       </c>
       <c r="R29" t="n">
-        <v>6943660</v>
+        <v>6943786</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3827,7 +3839,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3837,12 +3849,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På stor asp</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3869,7 +3876,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119567682</v>
+        <v>119570777</v>
       </c>
       <c r="B30" t="n">
         <v>79607</v>
@@ -3905,14 +3912,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490645</v>
+        <v>490693</v>
       </c>
       <c r="R30" t="n">
-        <v>6943575</v>
+        <v>6943819</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3944,7 +3951,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3954,12 +3961,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Vid surhål /kallkälla</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3986,10 +3988,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119560972</v>
+        <v>119567445</v>
       </c>
       <c r="B31" t="n">
-        <v>90576</v>
+        <v>95455</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4002,21 +4004,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4026,10 +4028,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490865</v>
+        <v>490638</v>
       </c>
       <c r="R31" t="n">
-        <v>6943527</v>
+        <v>6943512</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4061,7 +4063,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4071,7 +4073,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4098,10 +4100,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119567943</v>
+        <v>119570130</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>56522</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4110,41 +4112,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490651</v>
+        <v>490580</v>
       </c>
       <c r="R32" t="n">
-        <v>6943582</v>
+        <v>6943769</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4173,7 +4184,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4183,7 +4194,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4210,7 +4221,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119566845</v>
+        <v>119561375</v>
       </c>
       <c r="B33" t="n">
         <v>78526</v>
@@ -4250,10 +4261,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490615</v>
+        <v>490834</v>
       </c>
       <c r="R33" t="n">
-        <v>6943447</v>
+        <v>6943520</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4285,7 +4296,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4295,7 +4306,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4322,10 +4333,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119567445</v>
+        <v>119561285</v>
       </c>
       <c r="B34" t="n">
-        <v>95455</v>
+        <v>90558</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4338,21 +4349,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4362,10 +4373,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490638</v>
+        <v>490846</v>
       </c>
       <c r="R34" t="n">
-        <v>6943512</v>
+        <v>6943525</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4397,7 +4408,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4407,7 +4418,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4434,10 +4445,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119560369</v>
+        <v>119568797</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4446,41 +4457,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490931</v>
+        <v>490501</v>
       </c>
       <c r="R35" t="n">
-        <v>6943570</v>
+        <v>6943638</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4509,7 +4529,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4519,7 +4539,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4546,10 +4566,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119562537</v>
+        <v>119566845</v>
       </c>
       <c r="B36" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4562,42 +4582,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490683</v>
+        <v>490615</v>
       </c>
       <c r="R36" t="n">
-        <v>6943465</v>
+        <v>6943447</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4626,7 +4641,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4636,7 +4651,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4663,10 +4678,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119566746</v>
+        <v>119562537</v>
       </c>
       <c r="B37" t="n">
-        <v>82305</v>
+        <v>57463</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4679,37 +4694,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490599</v>
+        <v>490683</v>
       </c>
       <c r="R37" t="n">
-        <v>6943415</v>
+        <v>6943465</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4738,7 +4758,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4748,7 +4768,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4775,10 +4795,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119570130</v>
+        <v>119570334</v>
       </c>
       <c r="B38" t="n">
-        <v>56522</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4787,50 +4807,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490580</v>
+        <v>490582</v>
       </c>
       <c r="R38" t="n">
-        <v>6943769</v>
+        <v>6943798</v>
       </c>
       <c r="S38" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4859,7 +4870,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4869,7 +4880,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4896,10 +4907,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119564989</v>
+        <v>119567265</v>
       </c>
       <c r="B39" t="n">
-        <v>82305</v>
+        <v>79636</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4908,38 +4919,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490648</v>
+        <v>490622</v>
       </c>
       <c r="R39" t="n">
-        <v>6943345</v>
+        <v>6943503</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4971,7 +4982,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4981,12 +4992,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Många mycket gamla granar längs stranden</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5013,10 +5019,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119568960</v>
+        <v>119573937</v>
       </c>
       <c r="B40" t="n">
-        <v>79643</v>
+        <v>90576</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5025,41 +5031,44 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490488</v>
+        <v>490506</v>
       </c>
       <c r="R40" t="n">
-        <v>6943660</v>
+        <v>6943700</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5086,27 +5095,18 @@
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>18:13</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>18:13</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5125,7 +5125,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119611906</v>
+        <v>119611914</v>
       </c>
       <c r="B41" t="n">
         <v>97907</v>
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490727</v>
+        <v>490694</v>
       </c>
       <c r="R41" t="n">
-        <v>6943794</v>
+        <v>6943829</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5232,10 +5232,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119612059</v>
+        <v>119611984</v>
       </c>
       <c r="B42" t="n">
-        <v>79636</v>
+        <v>74638</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5244,25 +5244,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490631</v>
+        <v>490643</v>
       </c>
       <c r="R42" t="n">
-        <v>6943742</v>
+        <v>6943759</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119611969</v>
+        <v>119605869</v>
       </c>
       <c r="B43" t="n">
-        <v>95455</v>
+        <v>79607</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5354,41 +5354,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490646</v>
+        <v>490678</v>
       </c>
       <c r="R43" t="n">
-        <v>6943773</v>
+        <v>6943630</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5415,18 +5411,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5445,10 +5450,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119611950</v>
+        <v>119603962</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5457,53 +5462,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490710</v>
+        <v>490609</v>
       </c>
       <c r="R44" t="n">
-        <v>6943807</v>
+        <v>6943775</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5530,18 +5523,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5560,10 +5562,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119598920</v>
+        <v>119611906</v>
       </c>
       <c r="B45" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5572,41 +5574,45 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490801</v>
+        <v>490727</v>
       </c>
       <c r="R45" t="n">
-        <v>6943688</v>
+        <v>6943794</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5633,27 +5639,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5672,10 +5669,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119605333</v>
+        <v>119611950</v>
       </c>
       <c r="B46" t="n">
-        <v>74638</v>
+        <v>97907</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5684,41 +5681,53 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490655</v>
+        <v>490710</v>
       </c>
       <c r="R46" t="n">
-        <v>6943683</v>
+        <v>6943807</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5745,27 +5754,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5784,10 +5784,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119598830</v>
+        <v>119611689</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5800,37 +5800,40 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490809</v>
+        <v>490801</v>
       </c>
       <c r="R47" t="n">
-        <v>6943632</v>
+        <v>6943720</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5857,27 +5860,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5896,10 +5890,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119612016</v>
+        <v>119605333</v>
       </c>
       <c r="B48" t="n">
-        <v>79607</v>
+        <v>74638</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5912,40 +5906,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490631</v>
+        <v>490655</v>
       </c>
       <c r="R48" t="n">
-        <v>6943742</v>
+        <v>6943683</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5972,18 +5963,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6002,10 +6002,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119611864</v>
+        <v>119599421</v>
       </c>
       <c r="B49" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6014,53 +6014,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490760</v>
+        <v>490822</v>
       </c>
       <c r="R49" t="n">
-        <v>6943743</v>
+        <v>6943695</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6087,18 +6075,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6117,10 +6114,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119611914</v>
+        <v>119603940</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
+        <v>79643</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6129,45 +6126,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490694</v>
+        <v>490609</v>
       </c>
       <c r="R50" t="n">
-        <v>6943829</v>
+        <v>6943769</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6194,18 +6187,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6224,7 +6226,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119611850</v>
+        <v>119612090</v>
       </c>
       <c r="B51" t="n">
         <v>97907</v>
@@ -6259,7 +6261,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6276,13 +6278,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490774</v>
+        <v>490631</v>
       </c>
       <c r="R51" t="n">
-        <v>6943748</v>
+        <v>6943742</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6445,10 +6447,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119601996</v>
+        <v>119599288</v>
       </c>
       <c r="B53" t="n">
-        <v>78263</v>
+        <v>74638</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6461,21 +6463,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6485,10 +6487,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490657</v>
+        <v>490822</v>
       </c>
       <c r="R53" t="n">
-        <v>6943791</v>
+        <v>6943695</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6520,7 +6522,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6530,7 +6532,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6557,10 +6559,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119605869</v>
+        <v>119598641</v>
       </c>
       <c r="B54" t="n">
-        <v>79607</v>
+        <v>74638</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6573,34 +6575,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490678</v>
+        <v>490892</v>
       </c>
       <c r="R54" t="n">
-        <v>6943630</v>
+        <v>6943588</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6632,7 +6634,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6642,7 +6644,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6669,10 +6671,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119599504</v>
+        <v>119598920</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6685,21 +6687,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6709,10 +6711,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490789</v>
+        <v>490801</v>
       </c>
       <c r="R55" t="n">
-        <v>6943691</v>
+        <v>6943688</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6744,7 +6746,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6754,7 +6756,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6781,10 +6783,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119599641</v>
+        <v>119612016</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6797,42 +6799,40 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490793</v>
+        <v>490631</v>
       </c>
       <c r="R56" t="n">
-        <v>6943720</v>
+        <v>6943742</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6859,27 +6859,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6898,10 +6889,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119603940</v>
+        <v>119599504</v>
       </c>
       <c r="B57" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6910,25 +6901,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6938,10 +6929,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490609</v>
+        <v>490789</v>
       </c>
       <c r="R57" t="n">
-        <v>6943769</v>
+        <v>6943691</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6973,7 +6964,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6983,7 +6974,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7010,10 +7001,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119602140</v>
+        <v>119599641</v>
       </c>
       <c r="B58" t="n">
-        <v>82305</v>
+        <v>57310</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7026,34 +7017,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490645</v>
+        <v>490793</v>
       </c>
       <c r="R58" t="n">
-        <v>6943768</v>
+        <v>6943720</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7085,7 +7081,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7095,7 +7091,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7122,10 +7118,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119612354</v>
+        <v>119611850</v>
       </c>
       <c r="B59" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7134,35 +7130,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7170,13 +7170,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490610</v>
+        <v>490774</v>
       </c>
       <c r="R59" t="n">
-        <v>6943724</v>
+        <v>6943748</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7208,17 +7208,13 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7237,10 +7233,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119600343</v>
+        <v>119598830</v>
       </c>
       <c r="B60" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7253,21 +7249,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7277,10 +7273,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490740</v>
+        <v>490809</v>
       </c>
       <c r="R60" t="n">
-        <v>6943762</v>
+        <v>6943632</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7312,7 +7308,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7322,7 +7318,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7349,10 +7345,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119603478</v>
+        <v>119611864</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7361,41 +7357,53 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490638</v>
+        <v>490760</v>
       </c>
       <c r="R61" t="n">
-        <v>6943741</v>
+        <v>6943743</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7422,27 +7430,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7461,10 +7460,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119599288</v>
+        <v>119603478</v>
       </c>
       <c r="B62" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7477,21 +7476,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7501,10 +7500,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490822</v>
+        <v>490638</v>
       </c>
       <c r="R62" t="n">
-        <v>6943695</v>
+        <v>6943741</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7536,7 +7535,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7546,7 +7545,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7573,10 +7572,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119602492</v>
+        <v>119601996</v>
       </c>
       <c r="B63" t="n">
-        <v>90580</v>
+        <v>78263</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7589,21 +7588,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7613,10 +7612,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490621</v>
+        <v>490657</v>
       </c>
       <c r="R63" t="n">
-        <v>6943759</v>
+        <v>6943791</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7648,7 +7647,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7658,7 +7657,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7685,7 +7684,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119599421</v>
+        <v>119602140</v>
       </c>
       <c r="B64" t="n">
         <v>82305</v>
@@ -7725,10 +7724,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490822</v>
+        <v>490645</v>
       </c>
       <c r="R64" t="n">
-        <v>6943695</v>
+        <v>6943768</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7760,7 +7759,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7770,7 +7769,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7797,10 +7796,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119605344</v>
+        <v>119602492</v>
       </c>
       <c r="B65" t="n">
-        <v>56522</v>
+        <v>90580</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7809,43 +7808,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490655</v>
+        <v>490621</v>
       </c>
       <c r="R65" t="n">
-        <v>6943683</v>
+        <v>6943759</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7877,7 +7871,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7887,7 +7881,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7914,10 +7908,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119612090</v>
+        <v>119612059</v>
       </c>
       <c r="B66" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7926,39 +7920,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8029,10 +8014,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119598641</v>
+        <v>119611969</v>
       </c>
       <c r="B67" t="n">
-        <v>74638</v>
+        <v>95455</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8045,37 +8030,41 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490892</v>
+        <v>490646</v>
       </c>
       <c r="R67" t="n">
-        <v>6943588</v>
+        <v>6943773</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8102,27 +8091,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8141,10 +8121,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119604081</v>
+        <v>119605344</v>
       </c>
       <c r="B68" t="n">
-        <v>79607</v>
+        <v>56522</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8153,38 +8133,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490614</v>
+        <v>490655</v>
       </c>
       <c r="R68" t="n">
-        <v>6943732</v>
+        <v>6943683</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8216,7 +8201,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8226,7 +8211,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8253,10 +8238,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119611984</v>
+        <v>119600343</v>
       </c>
       <c r="B69" t="n">
-        <v>74638</v>
+        <v>82305</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8269,40 +8254,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490643</v>
+        <v>490740</v>
       </c>
       <c r="R69" t="n">
-        <v>6943759</v>
+        <v>6943762</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8329,18 +8311,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8359,7 +8350,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119603962</v>
+        <v>119604081</v>
       </c>
       <c r="B70" t="n">
         <v>79607</v>
@@ -8399,10 +8390,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490609</v>
+        <v>490614</v>
       </c>
       <c r="R70" t="n">
-        <v>6943775</v>
+        <v>6943732</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8434,7 +8425,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8444,7 +8435,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8471,10 +8462,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119611689</v>
+        <v>119612354</v>
       </c>
       <c r="B71" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8487,26 +8478,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8514,13 +8510,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490801</v>
+        <v>490610</v>
       </c>
       <c r="R71" t="n">
-        <v>6943720</v>
+        <v>6943724</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8552,13 +8548,17 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -2626,10 +2626,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119565821</v>
+        <v>119569440</v>
       </c>
       <c r="B19" t="n">
-        <v>74638</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2638,38 +2638,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490631</v>
+        <v>490493</v>
       </c>
       <c r="R19" t="n">
-        <v>6943382</v>
+        <v>6943708</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2701,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,7 +2720,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,10 +2747,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119569440</v>
+        <v>119565707</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,47 +2759,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490493</v>
+        <v>490616</v>
       </c>
       <c r="R20" t="n">
-        <v>6943708</v>
+        <v>6943373</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2859,10 +2859,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119565707</v>
+        <v>119565821</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2875,21 +2875,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490616</v>
+        <v>490631</v>
       </c>
       <c r="R21" t="n">
-        <v>6943373</v>
+        <v>6943382</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4795,10 +4795,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119570334</v>
+        <v>119573937</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4811,37 +4811,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490582</v>
+        <v>490506</v>
       </c>
       <c r="R38" t="n">
-        <v>6943798</v>
+        <v>6943700</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4868,27 +4871,18 @@
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>19:22</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>19:22</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4907,10 +4901,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119567265</v>
+        <v>119570334</v>
       </c>
       <c r="B39" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4919,38 +4913,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490622</v>
+        <v>490582</v>
       </c>
       <c r="R39" t="n">
-        <v>6943503</v>
+        <v>6943798</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4982,7 +4976,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4992,7 +4986,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5019,10 +5013,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119573937</v>
+        <v>119567265</v>
       </c>
       <c r="B40" t="n">
-        <v>90576</v>
+        <v>79636</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5031,44 +5025,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490506</v>
+        <v>490622</v>
       </c>
       <c r="R40" t="n">
-        <v>6943700</v>
+        <v>6943503</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5095,18 +5086,27 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -7233,10 +7233,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119598830</v>
+        <v>119611864</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7245,41 +7245,53 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490809</v>
+        <v>490760</v>
       </c>
       <c r="R60" t="n">
-        <v>6943632</v>
+        <v>6943743</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7306,27 +7318,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7345,10 +7348,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119611864</v>
+        <v>119598830</v>
       </c>
       <c r="B61" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7357,53 +7360,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490760</v>
+        <v>490809</v>
       </c>
       <c r="R61" t="n">
-        <v>6943743</v>
+        <v>6943632</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7430,18 +7421,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7460,10 +7460,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119603478</v>
+        <v>119601996</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7476,21 +7476,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490638</v>
+        <v>490657</v>
       </c>
       <c r="R62" t="n">
-        <v>6943741</v>
+        <v>6943791</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7572,10 +7572,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119601996</v>
+        <v>119603478</v>
       </c>
       <c r="B63" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7588,21 +7588,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490657</v>
+        <v>490638</v>
       </c>
       <c r="R63" t="n">
-        <v>6943791</v>
+        <v>6943741</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7908,10 +7908,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119612059</v>
+        <v>119611969</v>
       </c>
       <c r="B66" t="n">
-        <v>79636</v>
+        <v>95455</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7920,30 +7920,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>53</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7951,10 +7952,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490631</v>
+        <v>490646</v>
       </c>
       <c r="R66" t="n">
-        <v>6943742</v>
+        <v>6943773</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8014,10 +8015,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119611969</v>
+        <v>119612059</v>
       </c>
       <c r="B67" t="n">
-        <v>95455</v>
+        <v>79636</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8026,31 +8027,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490646</v>
+        <v>490631</v>
       </c>
       <c r="R67" t="n">
-        <v>6943773</v>
+        <v>6943742</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8121,10 +8121,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119605344</v>
+        <v>119604081</v>
       </c>
       <c r="B68" t="n">
-        <v>56522</v>
+        <v>79607</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8133,43 +8133,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490655</v>
+        <v>490614</v>
       </c>
       <c r="R68" t="n">
-        <v>6943683</v>
+        <v>6943732</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8201,7 +8196,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8211,7 +8206,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8350,10 +8345,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119604081</v>
+        <v>119605344</v>
       </c>
       <c r="B70" t="n">
-        <v>79607</v>
+        <v>56522</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8362,38 +8357,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490614</v>
+        <v>490655</v>
       </c>
       <c r="R70" t="n">
-        <v>6943732</v>
+        <v>6943683</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119564989</v>
+        <v>119569970</v>
       </c>
       <c r="B3" t="n">
-        <v>82305</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490648</v>
+        <v>490505</v>
       </c>
       <c r="R3" t="n">
-        <v>6943345</v>
+        <v>6943750</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Många mycket gamla granar längs stranden</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119568892</v>
+        <v>119562658</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490488</v>
+        <v>490654</v>
       </c>
       <c r="R4" t="n">
-        <v>6943660</v>
+        <v>6943443</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På stor asp</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119569122</v>
+        <v>119565821</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>74638</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,47 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490488</v>
+        <v>490631</v>
       </c>
       <c r="R5" t="n">
-        <v>6943685</v>
+        <v>6943382</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1105,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119568632</v>
+        <v>119573937</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>90576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,50 +1135,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490519</v>
+        <v>490506</v>
       </c>
       <c r="R6" t="n">
-        <v>6943605</v>
+        <v>6943700</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,27 +1199,18 @@
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1263,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119568960</v>
+        <v>119566746</v>
       </c>
       <c r="B7" t="n">
-        <v>79643</v>
+        <v>82305</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,38 +1241,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490488</v>
+        <v>490599</v>
       </c>
       <c r="R7" t="n">
-        <v>6943660</v>
+        <v>6943415</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1338,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119570068</v>
+        <v>119561285</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>90558</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,34 +1357,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490537</v>
+        <v>490846</v>
       </c>
       <c r="R8" t="n">
-        <v>6943742</v>
+        <v>6943525</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1450,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119567326</v>
+        <v>119565471</v>
       </c>
       <c r="B9" t="n">
-        <v>79635</v>
+        <v>74638</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,38 +1465,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490636</v>
+        <v>490635</v>
       </c>
       <c r="R9" t="n">
-        <v>6943499</v>
+        <v>6943355</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1562,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1538,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Många mycket gamla granar längs sjön</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119567682</v>
+        <v>119567326</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>79635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,25 +1582,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1639,10 +1610,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490645</v>
+        <v>490636</v>
       </c>
       <c r="R10" t="n">
-        <v>6943575</v>
+        <v>6943499</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1674,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,12 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Vid surhål /kallkälla</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119569847</v>
+        <v>119562305</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>79115</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,47 +1694,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490462</v>
+        <v>490757</v>
       </c>
       <c r="R11" t="n">
-        <v>6943718</v>
+        <v>6943439</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1800,7 +1757,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,7 +1767,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119560369</v>
+        <v>119563399</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,41 +1806,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490931</v>
+        <v>490675</v>
       </c>
       <c r="R12" t="n">
-        <v>6943570</v>
+        <v>6943404</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1912,7 +1878,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,7 +1888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119570901</v>
+        <v>119567978</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1965,21 +1931,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1989,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490713</v>
+        <v>490638</v>
       </c>
       <c r="R13" t="n">
-        <v>6943822</v>
+        <v>6943600</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2024,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2034,7 +2000,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119569970</v>
+        <v>119561375</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,34 +2043,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490505</v>
+        <v>490834</v>
       </c>
       <c r="R14" t="n">
-        <v>6943750</v>
+        <v>6943520</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2136,7 +2102,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2112,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119565471</v>
+        <v>119568960</v>
       </c>
       <c r="B15" t="n">
-        <v>74638</v>
+        <v>79643</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,38 +2151,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490635</v>
+        <v>490488</v>
       </c>
       <c r="R15" t="n">
-        <v>6943355</v>
+        <v>6943660</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2248,7 +2214,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2258,12 +2224,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Många mycket gamla granar längs sjön</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,10 +2251,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119566746</v>
+        <v>119570334</v>
       </c>
       <c r="B16" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,34 +2267,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490599</v>
+        <v>490582</v>
       </c>
       <c r="R16" t="n">
-        <v>6943415</v>
+        <v>6943798</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2365,7 +2326,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2375,7 +2336,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,10 +2363,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119567943</v>
+        <v>119570160</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,34 +2379,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490651</v>
+        <v>490561</v>
       </c>
       <c r="R17" t="n">
-        <v>6943582</v>
+        <v>6943765</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2477,7 +2438,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2448,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,10 +2475,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119562305</v>
+        <v>119568892</v>
       </c>
       <c r="B18" t="n">
-        <v>79115</v>
+        <v>79607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2530,34 +2491,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490757</v>
+        <v>490488</v>
       </c>
       <c r="R18" t="n">
-        <v>6943439</v>
+        <v>6943660</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2589,7 +2550,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2560,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På stor asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,10 +2592,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119569440</v>
+        <v>119570901</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2638,47 +2604,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490493</v>
+        <v>490713</v>
       </c>
       <c r="R19" t="n">
-        <v>6943708</v>
+        <v>6943822</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2710,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119565707</v>
+        <v>119568797</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2759,38 +2716,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490616</v>
+        <v>490501</v>
       </c>
       <c r="R20" t="n">
-        <v>6943373</v>
+        <v>6943638</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2822,7 +2788,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2832,7 +2798,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2859,10 +2825,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119565821</v>
+        <v>119567445</v>
       </c>
       <c r="B21" t="n">
-        <v>74638</v>
+        <v>95455</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2875,34 +2841,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490631</v>
+        <v>490638</v>
       </c>
       <c r="R21" t="n">
-        <v>6943382</v>
+        <v>6943512</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2934,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2944,7 +2910,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2971,7 +2937,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119570160</v>
+        <v>119570777</v>
       </c>
       <c r="B22" t="n">
         <v>79607</v>
@@ -3011,10 +2977,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490561</v>
+        <v>490693</v>
       </c>
       <c r="R22" t="n">
-        <v>6943765</v>
+        <v>6943819</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3046,7 +3012,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3056,7 +3022,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3083,10 +3049,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119567047</v>
+        <v>119565707</v>
       </c>
       <c r="B23" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3099,34 +3065,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490615</v>
+        <v>490616</v>
       </c>
       <c r="R23" t="n">
-        <v>6943448</v>
+        <v>6943373</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3158,7 +3124,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3168,7 +3134,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3195,10 +3161,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119563399</v>
+        <v>119567047</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>74638</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3207,47 +3173,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490675</v>
+        <v>490615</v>
       </c>
       <c r="R24" t="n">
-        <v>6943404</v>
+        <v>6943448</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3279,7 +3236,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3246,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3316,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119560972</v>
+        <v>119570068</v>
       </c>
       <c r="B25" t="n">
-        <v>90576</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3332,34 +3289,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490865</v>
+        <v>490537</v>
       </c>
       <c r="R25" t="n">
-        <v>6943527</v>
+        <v>6943742</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3391,7 +3348,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3401,7 +3358,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3428,10 +3385,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119566592</v>
+        <v>119567265</v>
       </c>
       <c r="B26" t="n">
-        <v>74638</v>
+        <v>79636</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3440,38 +3397,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490606</v>
+        <v>490622</v>
       </c>
       <c r="R26" t="n">
-        <v>6943414</v>
+        <v>6943503</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3503,7 +3460,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3513,7 +3470,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3540,10 +3497,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119562658</v>
+        <v>119564989</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,34 +3513,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490654</v>
+        <v>490648</v>
       </c>
       <c r="R27" t="n">
-        <v>6943443</v>
+        <v>6943345</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3615,7 +3572,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3625,7 +3582,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Många mycket gamla granar längs stranden</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3652,7 +3614,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119567978</v>
+        <v>119567682</v>
       </c>
       <c r="B28" t="n">
         <v>79607</v>
@@ -3692,10 +3654,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490638</v>
+        <v>490645</v>
       </c>
       <c r="R28" t="n">
-        <v>6943600</v>
+        <v>6943575</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3727,7 +3689,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3737,7 +3699,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Vid surhål /kallkälla</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3764,10 +3731,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119570243</v>
+        <v>119569847</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3776,38 +3743,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490559</v>
+        <v>490462</v>
       </c>
       <c r="R29" t="n">
-        <v>6943786</v>
+        <v>6943718</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3839,7 +3815,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3849,7 +3825,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3876,10 +3852,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119570777</v>
+        <v>119569440</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3888,38 +3864,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490693</v>
+        <v>490493</v>
       </c>
       <c r="R30" t="n">
-        <v>6943819</v>
+        <v>6943708</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3951,7 +3936,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3961,7 +3946,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3988,10 +3973,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119567445</v>
+        <v>119566845</v>
       </c>
       <c r="B31" t="n">
-        <v>95455</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4004,21 +3989,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4028,10 +4013,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490638</v>
+        <v>490615</v>
       </c>
       <c r="R31" t="n">
-        <v>6943512</v>
+        <v>6943447</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4063,7 +4048,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4073,7 +4058,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4100,10 +4085,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119570130</v>
+        <v>119569122</v>
       </c>
       <c r="B32" t="n">
-        <v>56522</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4112,50 +4097,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490580</v>
+        <v>490488</v>
       </c>
       <c r="R32" t="n">
-        <v>6943769</v>
+        <v>6943685</v>
       </c>
       <c r="S32" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4184,7 +4169,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4194,7 +4179,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4221,7 +4206,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119561375</v>
+        <v>119567943</v>
       </c>
       <c r="B33" t="n">
         <v>78526</v>
@@ -4261,10 +4246,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490834</v>
+        <v>490651</v>
       </c>
       <c r="R33" t="n">
-        <v>6943520</v>
+        <v>6943582</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4296,7 +4281,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4306,7 +4291,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4333,10 +4318,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119561285</v>
+        <v>119560369</v>
       </c>
       <c r="B34" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4349,21 +4334,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4373,13 +4358,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490846</v>
+        <v>490931</v>
       </c>
       <c r="R34" t="n">
-        <v>6943525</v>
+        <v>6943570</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4408,7 +4393,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4418,7 +4403,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4445,10 +4430,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119568797</v>
+        <v>119562537</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4457,50 +4442,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490501</v>
+        <v>490683</v>
       </c>
       <c r="R35" t="n">
-        <v>6943638</v>
+        <v>6943465</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4529,7 +4510,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4539,7 +4520,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4566,10 +4547,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119566845</v>
+        <v>119560972</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4582,21 +4563,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4606,10 +4587,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490615</v>
+        <v>490865</v>
       </c>
       <c r="R36" t="n">
-        <v>6943447</v>
+        <v>6943527</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4641,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4651,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4678,10 +4659,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119562537</v>
+        <v>119568632</v>
       </c>
       <c r="B37" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4690,46 +4671,50 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490683</v>
+        <v>490519</v>
       </c>
       <c r="R37" t="n">
-        <v>6943465</v>
+        <v>6943605</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4758,7 +4743,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4768,7 +4753,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4795,10 +4780,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119573937</v>
+        <v>119566592</v>
       </c>
       <c r="B38" t="n">
-        <v>90576</v>
+        <v>74638</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4811,40 +4796,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490506</v>
+        <v>490606</v>
       </c>
       <c r="R38" t="n">
-        <v>6943700</v>
+        <v>6943414</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4871,18 +4853,27 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4901,10 +4892,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119570334</v>
+        <v>119570243</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4917,21 +4908,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4941,10 +4932,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490582</v>
+        <v>490559</v>
       </c>
       <c r="R39" t="n">
-        <v>6943798</v>
+        <v>6943786</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4976,7 +4967,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4986,7 +4977,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5013,10 +5004,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119567265</v>
+        <v>119570130</v>
       </c>
       <c r="B40" t="n">
-        <v>79636</v>
+        <v>56522</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5029,37 +5020,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490622</v>
+        <v>490580</v>
       </c>
       <c r="R40" t="n">
-        <v>6943503</v>
+        <v>6943769</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5125,10 +5125,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119611914</v>
+        <v>119602492</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5137,45 +5137,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490694</v>
+        <v>490621</v>
       </c>
       <c r="R41" t="n">
-        <v>6943829</v>
+        <v>6943759</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5202,18 +5198,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5232,10 +5237,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119611984</v>
+        <v>119611864</v>
       </c>
       <c r="B42" t="n">
-        <v>74638</v>
+        <v>97907</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5244,30 +5249,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5275,10 +5289,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490643</v>
+        <v>490760</v>
       </c>
       <c r="R42" t="n">
-        <v>6943759</v>
+        <v>6943743</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5338,10 +5352,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119605869</v>
+        <v>119611914</v>
       </c>
       <c r="B43" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5350,41 +5364,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490678</v>
+        <v>490694</v>
       </c>
       <c r="R43" t="n">
-        <v>6943630</v>
+        <v>6943829</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5411,27 +5429,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5450,7 +5459,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119603962</v>
+        <v>119598920</v>
       </c>
       <c r="B44" t="n">
         <v>79607</v>
@@ -5490,10 +5499,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490609</v>
+        <v>490801</v>
       </c>
       <c r="R44" t="n">
-        <v>6943775</v>
+        <v>6943688</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5525,7 +5534,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5535,7 +5544,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5562,10 +5571,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119611906</v>
+        <v>119605344</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>56522</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5574,45 +5583,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490727</v>
+        <v>490655</v>
       </c>
       <c r="R45" t="n">
-        <v>6943794</v>
+        <v>6943683</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5639,18 +5649,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5669,7 +5688,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119611950</v>
+        <v>119612090</v>
       </c>
       <c r="B46" t="n">
         <v>97907</v>
@@ -5704,7 +5723,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5721,10 +5740,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490710</v>
+        <v>490631</v>
       </c>
       <c r="R46" t="n">
-        <v>6943807</v>
+        <v>6943742</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5784,10 +5803,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119611689</v>
+        <v>119601996</v>
       </c>
       <c r="B47" t="n">
-        <v>79607</v>
+        <v>78263</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5800,40 +5819,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490801</v>
+        <v>490657</v>
       </c>
       <c r="R47" t="n">
-        <v>6943720</v>
+        <v>6943791</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5860,18 +5876,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5890,10 +5915,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119605333</v>
+        <v>119611950</v>
       </c>
       <c r="B48" t="n">
-        <v>74638</v>
+        <v>97907</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5902,41 +5927,53 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490655</v>
+        <v>490710</v>
       </c>
       <c r="R48" t="n">
-        <v>6943683</v>
+        <v>6943807</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5963,27 +6000,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6002,10 +6030,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119599421</v>
+        <v>119611850</v>
       </c>
       <c r="B49" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6014,41 +6042,53 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490822</v>
+        <v>490774</v>
       </c>
       <c r="R49" t="n">
-        <v>6943695</v>
+        <v>6943748</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6075,27 +6115,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6114,10 +6145,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119603940</v>
+        <v>119611984</v>
       </c>
       <c r="B50" t="n">
-        <v>79643</v>
+        <v>74638</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6126,41 +6157,44 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490609</v>
+        <v>490643</v>
       </c>
       <c r="R50" t="n">
-        <v>6943769</v>
+        <v>6943759</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6187,27 +6221,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6226,10 +6251,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119612090</v>
+        <v>119612016</v>
       </c>
       <c r="B51" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6238,39 +6263,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6341,10 +6357,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119611930</v>
+        <v>119602140</v>
       </c>
       <c r="B52" t="n">
-        <v>90576</v>
+        <v>82305</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6357,40 +6373,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490703</v>
+        <v>490645</v>
       </c>
       <c r="R52" t="n">
-        <v>6943806</v>
+        <v>6943768</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6417,18 +6430,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6447,10 +6469,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119599288</v>
+        <v>119611906</v>
       </c>
       <c r="B53" t="n">
-        <v>74638</v>
+        <v>97907</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6459,41 +6481,45 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490822</v>
+        <v>490727</v>
       </c>
       <c r="R53" t="n">
-        <v>6943695</v>
+        <v>6943794</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6520,27 +6546,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6559,10 +6576,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119598641</v>
+        <v>119599504</v>
       </c>
       <c r="B54" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6575,34 +6592,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490892</v>
+        <v>490789</v>
       </c>
       <c r="R54" t="n">
-        <v>6943588</v>
+        <v>6943691</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6634,7 +6651,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6644,7 +6661,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6671,10 +6688,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119598920</v>
+        <v>119599288</v>
       </c>
       <c r="B55" t="n">
-        <v>79607</v>
+        <v>74638</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6687,21 +6704,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6711,10 +6728,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490801</v>
+        <v>490822</v>
       </c>
       <c r="R55" t="n">
-        <v>6943688</v>
+        <v>6943695</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6746,7 +6763,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6756,7 +6773,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6783,10 +6800,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119612016</v>
+        <v>119598830</v>
       </c>
       <c r="B56" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6799,40 +6816,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490631</v>
+        <v>490809</v>
       </c>
       <c r="R56" t="n">
-        <v>6943742</v>
+        <v>6943632</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6859,18 +6873,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6889,10 +6912,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119599504</v>
+        <v>119605869</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6905,21 +6928,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6929,10 +6952,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490789</v>
+        <v>490678</v>
       </c>
       <c r="R57" t="n">
-        <v>6943691</v>
+        <v>6943630</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6964,7 +6987,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6974,7 +6997,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7118,10 +7141,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119611850</v>
+        <v>119612059</v>
       </c>
       <c r="B59" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7130,39 +7153,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7170,13 +7184,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490774</v>
+        <v>490631</v>
       </c>
       <c r="R59" t="n">
-        <v>6943748</v>
+        <v>6943742</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7233,10 +7247,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119611864</v>
+        <v>119604081</v>
       </c>
       <c r="B60" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7245,53 +7259,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490760</v>
+        <v>490614</v>
       </c>
       <c r="R60" t="n">
-        <v>6943743</v>
+        <v>6943732</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7318,18 +7320,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7348,10 +7359,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119598830</v>
+        <v>119599421</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7364,21 +7375,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7388,10 +7399,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490809</v>
+        <v>490822</v>
       </c>
       <c r="R61" t="n">
-        <v>6943632</v>
+        <v>6943695</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7423,7 +7434,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7433,7 +7444,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7460,10 +7471,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119601996</v>
+        <v>119603478</v>
       </c>
       <c r="B62" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7476,21 +7487,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7500,10 +7511,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490657</v>
+        <v>490638</v>
       </c>
       <c r="R62" t="n">
-        <v>6943791</v>
+        <v>6943741</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7535,7 +7546,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7545,7 +7556,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7572,10 +7583,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119603478</v>
+        <v>119600343</v>
       </c>
       <c r="B63" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7588,21 +7599,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7612,10 +7623,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490638</v>
+        <v>490740</v>
       </c>
       <c r="R63" t="n">
-        <v>6943741</v>
+        <v>6943762</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7647,7 +7658,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7657,7 +7668,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7684,10 +7695,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119602140</v>
+        <v>119611969</v>
       </c>
       <c r="B64" t="n">
-        <v>82305</v>
+        <v>95455</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7700,37 +7711,41 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490645</v>
+        <v>490646</v>
       </c>
       <c r="R64" t="n">
-        <v>6943768</v>
+        <v>6943773</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7757,27 +7772,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7796,10 +7802,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119602492</v>
+        <v>119611689</v>
       </c>
       <c r="B65" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7812,37 +7818,40 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490621</v>
+        <v>490801</v>
       </c>
       <c r="R65" t="n">
-        <v>6943759</v>
+        <v>6943720</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7869,27 +7878,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7908,10 +7908,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119611969</v>
+        <v>119612354</v>
       </c>
       <c r="B66" t="n">
-        <v>95455</v>
+        <v>57310</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7924,27 +7924,31 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7952,10 +7956,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490646</v>
+        <v>490610</v>
       </c>
       <c r="R66" t="n">
-        <v>6943773</v>
+        <v>6943724</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7990,13 +7994,17 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8015,10 +8023,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119612059</v>
+        <v>119611930</v>
       </c>
       <c r="B67" t="n">
-        <v>79636</v>
+        <v>90576</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8027,25 +8035,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8058,10 +8066,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490631</v>
+        <v>490703</v>
       </c>
       <c r="R67" t="n">
-        <v>6943742</v>
+        <v>6943806</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8121,10 +8129,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119604081</v>
+        <v>119603940</v>
       </c>
       <c r="B68" t="n">
-        <v>79607</v>
+        <v>79643</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8133,25 +8141,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8161,10 +8169,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490614</v>
+        <v>490609</v>
       </c>
       <c r="R68" t="n">
-        <v>6943732</v>
+        <v>6943769</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8196,7 +8204,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8206,7 +8214,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8233,10 +8241,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119600343</v>
+        <v>119598641</v>
       </c>
       <c r="B69" t="n">
-        <v>82305</v>
+        <v>74638</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8249,34 +8257,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490740</v>
+        <v>490892</v>
       </c>
       <c r="R69" t="n">
-        <v>6943762</v>
+        <v>6943588</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -8308,7 +8316,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8318,7 +8326,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8345,10 +8353,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119605344</v>
+        <v>119603962</v>
       </c>
       <c r="B70" t="n">
-        <v>56522</v>
+        <v>79607</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8357,43 +8365,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490655</v>
+        <v>490609</v>
       </c>
       <c r="R70" t="n">
-        <v>6943683</v>
+        <v>6943775</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8425,7 +8428,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8435,7 +8438,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8462,10 +8465,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119612354</v>
+        <v>119605333</v>
       </c>
       <c r="B71" t="n">
-        <v>57310</v>
+        <v>74638</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8478,45 +8481,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490610</v>
+        <v>490655</v>
       </c>
       <c r="R71" t="n">
-        <v>6943724</v>
+        <v>6943683</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8543,14 +8538,19 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -2139,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119568960</v>
+        <v>119570160</v>
       </c>
       <c r="B15" t="n">
-        <v>79643</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,38 +2151,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490488</v>
+        <v>490561</v>
       </c>
       <c r="R15" t="n">
-        <v>6943660</v>
+        <v>6943765</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,7 +2251,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119570334</v>
+        <v>119570901</v>
       </c>
       <c r="B16" t="n">
         <v>78526</v>
@@ -2287,14 +2287,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490582</v>
+        <v>490713</v>
       </c>
       <c r="R16" t="n">
-        <v>6943798</v>
+        <v>6943822</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,10 +2363,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119570160</v>
+        <v>119568797</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2375,38 +2375,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490561</v>
+        <v>490501</v>
       </c>
       <c r="R17" t="n">
-        <v>6943765</v>
+        <v>6943638</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2438,7 +2447,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2448,7 +2457,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2475,10 +2484,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119568892</v>
+        <v>119567445</v>
       </c>
       <c r="B18" t="n">
-        <v>79607</v>
+        <v>95455</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2491,34 +2500,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490488</v>
+        <v>490638</v>
       </c>
       <c r="R18" t="n">
-        <v>6943660</v>
+        <v>6943512</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2550,7 +2559,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2560,12 +2569,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På stor asp</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,10 +2596,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119570901</v>
+        <v>119568960</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,38 +2608,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490713</v>
+        <v>490488</v>
       </c>
       <c r="R19" t="n">
-        <v>6943822</v>
+        <v>6943660</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2667,7 +2671,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2681,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2708,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119568797</v>
+        <v>119570334</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2716,47 +2720,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490501</v>
+        <v>490582</v>
       </c>
       <c r="R20" t="n">
-        <v>6943638</v>
+        <v>6943798</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2788,7 +2783,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2798,7 +2793,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,10 +2820,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119567445</v>
+        <v>119568892</v>
       </c>
       <c r="B21" t="n">
-        <v>95455</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2841,34 +2836,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490638</v>
+        <v>490488</v>
       </c>
       <c r="R21" t="n">
-        <v>6943512</v>
+        <v>6943660</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2900,7 +2895,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,7 +2905,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På stor asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119567943</v>
+        <v>119568632</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4218,38 +4218,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490651</v>
+        <v>490519</v>
       </c>
       <c r="R33" t="n">
-        <v>6943582</v>
+        <v>6943605</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4281,7 +4290,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4291,7 +4300,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4318,10 +4327,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119560369</v>
+        <v>119560972</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4334,21 +4343,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4358,13 +4367,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490931</v>
+        <v>490865</v>
       </c>
       <c r="R34" t="n">
-        <v>6943570</v>
+        <v>6943527</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4393,7 +4402,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4403,7 +4412,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4430,10 +4439,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119562537</v>
+        <v>119567943</v>
       </c>
       <c r="B35" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4446,42 +4455,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490683</v>
+        <v>490651</v>
       </c>
       <c r="R35" t="n">
-        <v>6943465</v>
+        <v>6943582</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4510,7 +4514,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4520,7 +4524,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4547,10 +4551,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119560972</v>
+        <v>119560369</v>
       </c>
       <c r="B36" t="n">
-        <v>90576</v>
+        <v>78526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4563,21 +4567,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4587,13 +4591,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490865</v>
+        <v>490931</v>
       </c>
       <c r="R36" t="n">
-        <v>6943527</v>
+        <v>6943570</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4622,7 +4626,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4636,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4659,10 +4663,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119568632</v>
+        <v>119562537</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4671,50 +4675,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490519</v>
+        <v>490683</v>
       </c>
       <c r="R37" t="n">
-        <v>6943605</v>
+        <v>6943465</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5352,10 +5352,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119611914</v>
+        <v>119598920</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5364,45 +5364,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490694</v>
+        <v>490801</v>
       </c>
       <c r="R43" t="n">
-        <v>6943829</v>
+        <v>6943688</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5429,18 +5425,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5459,10 +5464,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119598920</v>
+        <v>119605344</v>
       </c>
       <c r="B44" t="n">
-        <v>79607</v>
+        <v>56522</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5471,38 +5476,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490801</v>
+        <v>490655</v>
       </c>
       <c r="R44" t="n">
-        <v>6943688</v>
+        <v>6943683</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5534,7 +5544,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5544,7 +5554,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5571,10 +5581,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119605344</v>
+        <v>119611914</v>
       </c>
       <c r="B45" t="n">
-        <v>56522</v>
+        <v>97907</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5583,46 +5593,45 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490655</v>
+        <v>490694</v>
       </c>
       <c r="R45" t="n">
-        <v>6943683</v>
+        <v>6943829</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5649,27 +5658,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>16:44</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>16:44</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5803,10 +5803,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119601996</v>
+        <v>119611950</v>
       </c>
       <c r="B47" t="n">
-        <v>78263</v>
+        <v>97907</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5815,41 +5815,53 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490657</v>
+        <v>490710</v>
       </c>
       <c r="R47" t="n">
-        <v>6943791</v>
+        <v>6943807</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5876,27 +5888,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5915,7 +5918,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119611950</v>
+        <v>119611850</v>
       </c>
       <c r="B48" t="n">
         <v>97907</v>
@@ -5950,7 +5953,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5967,13 +5970,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490710</v>
+        <v>490774</v>
       </c>
       <c r="R48" t="n">
-        <v>6943807</v>
+        <v>6943748</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6030,10 +6033,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119611850</v>
+        <v>119601996</v>
       </c>
       <c r="B49" t="n">
-        <v>97907</v>
+        <v>78263</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6042,53 +6045,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490774</v>
+        <v>490657</v>
       </c>
       <c r="R49" t="n">
-        <v>6943748</v>
+        <v>6943791</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6115,18 +6106,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -7471,10 +7471,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119603478</v>
+        <v>119600343</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7487,21 +7487,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7511,10 +7511,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490638</v>
+        <v>490740</v>
       </c>
       <c r="R62" t="n">
-        <v>6943741</v>
+        <v>6943762</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7583,10 +7583,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119600343</v>
+        <v>119603478</v>
       </c>
       <c r="B63" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7599,21 +7599,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7623,10 +7623,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490740</v>
+        <v>490638</v>
       </c>
       <c r="R63" t="n">
-        <v>6943762</v>
+        <v>6943741</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -5125,10 +5125,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119602492</v>
+        <v>119611930</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5141,37 +5141,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490621</v>
+        <v>490703</v>
       </c>
       <c r="R41" t="n">
-        <v>6943759</v>
+        <v>6943806</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5198,27 +5201,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5237,10 +5231,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119611864</v>
+        <v>119604081</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5249,53 +5243,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490760</v>
+        <v>490614</v>
       </c>
       <c r="R42" t="n">
-        <v>6943743</v>
+        <v>6943732</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5322,18 +5304,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5352,7 +5343,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119598920</v>
+        <v>119612016</v>
       </c>
       <c r="B43" t="n">
         <v>79607</v>
@@ -5386,19 +5377,22 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490801</v>
+        <v>490631</v>
       </c>
       <c r="R43" t="n">
-        <v>6943688</v>
+        <v>6943742</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5425,27 +5419,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5464,10 +5449,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119605344</v>
+        <v>119603478</v>
       </c>
       <c r="B44" t="n">
-        <v>56522</v>
+        <v>78526</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5476,43 +5461,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490655</v>
+        <v>490638</v>
       </c>
       <c r="R44" t="n">
-        <v>6943683</v>
+        <v>6943741</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5544,7 +5524,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5554,7 +5534,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5581,10 +5561,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119611914</v>
+        <v>119602140</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5593,45 +5573,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490694</v>
+        <v>490645</v>
       </c>
       <c r="R45" t="n">
-        <v>6943829</v>
+        <v>6943768</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5658,18 +5634,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5688,10 +5673,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119612090</v>
+        <v>119611984</v>
       </c>
       <c r="B46" t="n">
-        <v>97907</v>
+        <v>74638</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5700,39 +5685,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5740,10 +5716,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490631</v>
+        <v>490643</v>
       </c>
       <c r="R46" t="n">
-        <v>6943742</v>
+        <v>6943759</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5803,7 +5779,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119611950</v>
+        <v>119611906</v>
       </c>
       <c r="B47" t="n">
         <v>97907</v>
@@ -5836,16 +5812,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -5855,10 +5823,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490710</v>
+        <v>490727</v>
       </c>
       <c r="R47" t="n">
-        <v>6943807</v>
+        <v>6943794</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5918,7 +5886,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119611850</v>
+        <v>119611914</v>
       </c>
       <c r="B48" t="n">
         <v>97907</v>
@@ -5951,16 +5919,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -5970,13 +5930,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490774</v>
+        <v>490694</v>
       </c>
       <c r="R48" t="n">
-        <v>6943748</v>
+        <v>6943829</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6033,10 +5993,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119601996</v>
+        <v>119599641</v>
       </c>
       <c r="B49" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6049,34 +6009,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490657</v>
+        <v>490793</v>
       </c>
       <c r="R49" t="n">
-        <v>6943791</v>
+        <v>6943720</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6108,7 +6073,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6118,7 +6083,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6145,7 +6110,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119611984</v>
+        <v>119599288</v>
       </c>
       <c r="B50" t="n">
         <v>74638</v>
@@ -6179,22 +6144,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490643</v>
+        <v>490822</v>
       </c>
       <c r="R50" t="n">
-        <v>6943759</v>
+        <v>6943695</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6221,18 +6183,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6251,10 +6222,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119612016</v>
+        <v>119611969</v>
       </c>
       <c r="B51" t="n">
-        <v>79607</v>
+        <v>95455</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6267,26 +6238,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6294,10 +6266,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490631</v>
+        <v>490646</v>
       </c>
       <c r="R51" t="n">
-        <v>6943742</v>
+        <v>6943773</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6357,10 +6329,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119602140</v>
+        <v>119611864</v>
       </c>
       <c r="B52" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6369,41 +6341,53 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490645</v>
+        <v>490760</v>
       </c>
       <c r="R52" t="n">
-        <v>6943768</v>
+        <v>6943743</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6430,27 +6414,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6469,10 +6444,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119611906</v>
+        <v>119598830</v>
       </c>
       <c r="B53" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6481,45 +6456,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490727</v>
+        <v>490809</v>
       </c>
       <c r="R53" t="n">
-        <v>6943794</v>
+        <v>6943632</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6546,18 +6517,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6576,10 +6556,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119599504</v>
+        <v>119603940</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6588,25 +6568,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6616,10 +6596,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490789</v>
+        <v>490609</v>
       </c>
       <c r="R54" t="n">
-        <v>6943691</v>
+        <v>6943769</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6651,7 +6631,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6661,7 +6641,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6688,10 +6668,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119599288</v>
+        <v>119600343</v>
       </c>
       <c r="B55" t="n">
-        <v>74638</v>
+        <v>82305</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6704,21 +6684,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6728,10 +6708,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490822</v>
+        <v>490740</v>
       </c>
       <c r="R55" t="n">
-        <v>6943695</v>
+        <v>6943762</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6763,7 +6743,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6773,7 +6753,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6800,10 +6780,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119598830</v>
+        <v>119603962</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6816,21 +6796,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6840,10 +6820,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490809</v>
+        <v>490609</v>
       </c>
       <c r="R56" t="n">
-        <v>6943632</v>
+        <v>6943775</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6875,7 +6855,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6885,7 +6865,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6912,10 +6892,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119605869</v>
+        <v>119612354</v>
       </c>
       <c r="B57" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6928,37 +6908,45 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490678</v>
+        <v>490610</v>
       </c>
       <c r="R57" t="n">
-        <v>6943630</v>
+        <v>6943724</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6985,19 +6973,14 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>17:00</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7024,10 +7007,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119599641</v>
+        <v>119602492</v>
       </c>
       <c r="B58" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7040,39 +7023,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490793</v>
+        <v>490621</v>
       </c>
       <c r="R58" t="n">
-        <v>6943720</v>
+        <v>6943759</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7104,7 +7082,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7114,7 +7092,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7141,10 +7119,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119612059</v>
+        <v>119598920</v>
       </c>
       <c r="B59" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7153,44 +7131,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490631</v>
+        <v>490801</v>
       </c>
       <c r="R59" t="n">
-        <v>6943742</v>
+        <v>6943688</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7217,18 +7192,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7247,7 +7231,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119604081</v>
+        <v>119605869</v>
       </c>
       <c r="B60" t="n">
         <v>79607</v>
@@ -7287,10 +7271,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490614</v>
+        <v>490678</v>
       </c>
       <c r="R60" t="n">
-        <v>6943732</v>
+        <v>6943630</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7322,7 +7306,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7332,7 +7316,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7359,10 +7343,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119599421</v>
+        <v>119612090</v>
       </c>
       <c r="B61" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7371,41 +7355,53 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490822</v>
+        <v>490631</v>
       </c>
       <c r="R61" t="n">
-        <v>6943695</v>
+        <v>6943742</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7432,27 +7428,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7471,10 +7458,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119600343</v>
+        <v>119611950</v>
       </c>
       <c r="B62" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7483,41 +7470,53 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490740</v>
+        <v>490710</v>
       </c>
       <c r="R62" t="n">
-        <v>6943762</v>
+        <v>6943807</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7544,27 +7543,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7583,10 +7573,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119603478</v>
+        <v>119611850</v>
       </c>
       <c r="B63" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7595,41 +7585,53 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490638</v>
+        <v>490774</v>
       </c>
       <c r="R63" t="n">
-        <v>6943741</v>
+        <v>6943748</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7656,27 +7658,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7695,10 +7688,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119611969</v>
+        <v>119599421</v>
       </c>
       <c r="B64" t="n">
-        <v>95455</v>
+        <v>82305</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7711,41 +7704,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490646</v>
+        <v>490822</v>
       </c>
       <c r="R64" t="n">
-        <v>6943773</v>
+        <v>6943695</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7772,18 +7761,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7802,10 +7800,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119611689</v>
+        <v>119599504</v>
       </c>
       <c r="B65" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7818,40 +7816,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490801</v>
+        <v>490789</v>
       </c>
       <c r="R65" t="n">
-        <v>6943720</v>
+        <v>6943691</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7878,18 +7873,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7908,10 +7912,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119612354</v>
+        <v>119605344</v>
       </c>
       <c r="B66" t="n">
-        <v>57310</v>
+        <v>56522</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7920,49 +7924,46 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490610</v>
+        <v>490655</v>
       </c>
       <c r="R66" t="n">
-        <v>6943724</v>
+        <v>6943683</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7989,14 +7990,19 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8023,10 +8029,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119611930</v>
+        <v>119598641</v>
       </c>
       <c r="B67" t="n">
-        <v>90576</v>
+        <v>74638</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8039,40 +8045,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490703</v>
+        <v>490892</v>
       </c>
       <c r="R67" t="n">
-        <v>6943806</v>
+        <v>6943588</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8099,18 +8102,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8129,10 +8141,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119603940</v>
+        <v>119601996</v>
       </c>
       <c r="B68" t="n">
-        <v>79643</v>
+        <v>78263</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8141,25 +8153,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8169,10 +8181,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490609</v>
+        <v>490657</v>
       </c>
       <c r="R68" t="n">
-        <v>6943769</v>
+        <v>6943791</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8204,7 +8216,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8214,7 +8226,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8241,10 +8253,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119598641</v>
+        <v>119612059</v>
       </c>
       <c r="B69" t="n">
-        <v>74638</v>
+        <v>79636</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8253,41 +8265,44 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490892</v>
+        <v>490631</v>
       </c>
       <c r="R69" t="n">
-        <v>6943588</v>
+        <v>6943742</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8314,27 +8329,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8353,10 +8359,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119603962</v>
+        <v>119605333</v>
       </c>
       <c r="B70" t="n">
-        <v>79607</v>
+        <v>74638</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8369,21 +8375,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8393,10 +8399,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490609</v>
+        <v>490655</v>
       </c>
       <c r="R70" t="n">
-        <v>6943775</v>
+        <v>6943683</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8428,7 +8434,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8438,7 +8444,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8465,10 +8471,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119605333</v>
+        <v>119611689</v>
       </c>
       <c r="B71" t="n">
-        <v>74638</v>
+        <v>79607</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8481,37 +8487,40 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490655</v>
+        <v>490801</v>
       </c>
       <c r="R71" t="n">
-        <v>6943683</v>
+        <v>6943720</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8538,27 +8547,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -5561,10 +5561,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119602140</v>
+        <v>119611984</v>
       </c>
       <c r="B45" t="n">
-        <v>82305</v>
+        <v>74638</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5577,37 +5577,40 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490645</v>
+        <v>490643</v>
       </c>
       <c r="R45" t="n">
-        <v>6943768</v>
+        <v>6943759</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5634,27 +5637,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5673,10 +5667,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119611984</v>
+        <v>119602140</v>
       </c>
       <c r="B46" t="n">
-        <v>74638</v>
+        <v>82305</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5689,40 +5683,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490643</v>
+        <v>490645</v>
       </c>
       <c r="R46" t="n">
-        <v>6943759</v>
+        <v>6943768</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5749,18 +5740,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6668,10 +6668,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119600343</v>
+        <v>119603962</v>
       </c>
       <c r="B55" t="n">
-        <v>82305</v>
+        <v>79607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6684,21 +6684,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6708,10 +6708,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490740</v>
+        <v>490609</v>
       </c>
       <c r="R55" t="n">
-        <v>6943762</v>
+        <v>6943775</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6780,10 +6780,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119603962</v>
+        <v>119600343</v>
       </c>
       <c r="B56" t="n">
-        <v>79607</v>
+        <v>82305</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6796,21 +6796,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490609</v>
+        <v>490740</v>
       </c>
       <c r="R56" t="n">
-        <v>6943775</v>
+        <v>6943762</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -8580,7 +8580,7 @@
         <v>119604751</v>
       </c>
       <c r="B72" t="n">
-        <v>95455</v>
+        <v>95478</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8687,6 +8687,1202 @@
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127302751</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91893</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>760</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>490726</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6943641</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127303436</v>
+      </c>
+      <c r="B74" t="n">
+        <v>75135</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>490658</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6943642</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127305232</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>490703</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6943512</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>21:28</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>21:28</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>127304100</v>
+      </c>
+      <c r="B76" t="n">
+        <v>80142</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>490611</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6943604</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127304206</v>
+      </c>
+      <c r="B77" t="n">
+        <v>80115</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>490622</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6943589</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127304672</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80114</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>490643</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6943554</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127302585</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>490729</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6943626</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>127303834</v>
+      </c>
+      <c r="B80" t="n">
+        <v>80114</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>490619</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6943643</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På död stående sälg med bohål och födospår från hackspett</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127305164</v>
+      </c>
+      <c r="B81" t="n">
+        <v>80114</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>490690</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6943499</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>21:24</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>21:24</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127304951</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>490646</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6943520</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127304399</v>
+      </c>
+      <c r="B83" t="n">
+        <v>97314</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>490621</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6943586</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Vid litet surdråg</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -8689,32 +8689,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127302751</v>
+        <v>127305232</v>
       </c>
       <c r="B73" t="n">
-        <v>91893</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490726</v>
+        <v>490703</v>
       </c>
       <c r="R73" t="n">
-        <v>6943641</v>
+        <v>6943512</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8796,32 +8796,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127303436</v>
+        <v>127302751</v>
       </c>
       <c r="B74" t="n">
-        <v>75135</v>
+        <v>91899</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>760</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490658</v>
+        <v>490726</v>
       </c>
       <c r="R74" t="n">
-        <v>6943642</v>
+        <v>6943641</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8903,10 +8903,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127305232</v>
+        <v>127303436</v>
       </c>
       <c r="B75" t="n">
-        <v>79011</v>
+        <v>75138</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8914,21 +8914,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490703</v>
+        <v>490658</v>
       </c>
       <c r="R75" t="n">
-        <v>6943512</v>
+        <v>6943642</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9013,7 +9013,7 @@
         <v>127304100</v>
       </c>
       <c r="B76" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>127304206</v>
       </c>
       <c r="B77" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>127304672</v>
       </c>
       <c r="B78" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>127302585</v>
       </c>
       <c r="B79" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>127303834</v>
       </c>
       <c r="B80" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>127305164</v>
       </c>
       <c r="B81" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>127304951</v>
       </c>
       <c r="B82" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>127304399</v>
       </c>
       <c r="B83" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -8689,32 +8689,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127305232</v>
+        <v>127302751</v>
       </c>
       <c r="B73" t="n">
-        <v>79014</v>
+        <v>91899</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490703</v>
+        <v>490726</v>
       </c>
       <c r="R73" t="n">
-        <v>6943512</v>
+        <v>6943641</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8796,32 +8796,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127302751</v>
+        <v>127305232</v>
       </c>
       <c r="B74" t="n">
-        <v>91899</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490726</v>
+        <v>490703</v>
       </c>
       <c r="R74" t="n">
-        <v>6943641</v>
+        <v>6943512</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -8692,7 +8692,7 @@
         <v>127302751</v>
       </c>
       <c r="B73" t="n">
-        <v>91899</v>
+        <v>91900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>127304951</v>
       </c>
       <c r="B82" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>127304399</v>
       </c>
       <c r="B83" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -8692,7 +8692,7 @@
         <v>127302751</v>
       </c>
       <c r="B73" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>127305232</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>127303436</v>
       </c>
       <c r="B75" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>127304100</v>
       </c>
       <c r="B76" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>127304206</v>
       </c>
       <c r="B77" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>127304672</v>
       </c>
       <c r="B78" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>127302585</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>127303834</v>
       </c>
       <c r="B80" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>127305164</v>
       </c>
       <c r="B81" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>127304951</v>
       </c>
       <c r="B82" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>127304399</v>
       </c>
       <c r="B83" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -8689,32 +8689,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127302751</v>
+        <v>127305232</v>
       </c>
       <c r="B73" t="n">
-        <v>91904</v>
+        <v>79018</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490726</v>
+        <v>490703</v>
       </c>
       <c r="R73" t="n">
-        <v>6943641</v>
+        <v>6943512</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8796,10 +8796,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127305232</v>
+        <v>127303436</v>
       </c>
       <c r="B74" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490703</v>
+        <v>490658</v>
       </c>
       <c r="R74" t="n">
-        <v>6943512</v>
+        <v>6943642</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8903,32 +8903,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127303436</v>
+        <v>127302751</v>
       </c>
       <c r="B75" t="n">
-        <v>75142</v>
+        <v>91904</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>760</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490658</v>
+        <v>490726</v>
       </c>
       <c r="R75" t="n">
-        <v>6943642</v>
+        <v>6943641</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -8689,32 +8689,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127305232</v>
+        <v>127302751</v>
       </c>
       <c r="B73" t="n">
-        <v>79018</v>
+        <v>91904</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490703</v>
+        <v>490726</v>
       </c>
       <c r="R73" t="n">
-        <v>6943512</v>
+        <v>6943641</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8796,10 +8796,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127303436</v>
+        <v>127305232</v>
       </c>
       <c r="B74" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490658</v>
+        <v>490703</v>
       </c>
       <c r="R74" t="n">
-        <v>6943642</v>
+        <v>6943512</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8903,32 +8903,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127302751</v>
+        <v>127303436</v>
       </c>
       <c r="B75" t="n">
-        <v>91904</v>
+        <v>75142</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>760</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490726</v>
+        <v>490658</v>
       </c>
       <c r="R75" t="n">
-        <v>6943641</v>
+        <v>6943642</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9660,7 +9660,7 @@
         <v>127304951</v>
       </c>
       <c r="B82" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -8689,32 +8689,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127302751</v>
+        <v>127305232</v>
       </c>
       <c r="B73" t="n">
-        <v>91904</v>
+        <v>79020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490726</v>
+        <v>490703</v>
       </c>
       <c r="R73" t="n">
-        <v>6943641</v>
+        <v>6943512</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8796,10 +8796,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127305232</v>
+        <v>127303436</v>
       </c>
       <c r="B74" t="n">
-        <v>79018</v>
+        <v>75144</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490703</v>
+        <v>490658</v>
       </c>
       <c r="R74" t="n">
-        <v>6943512</v>
+        <v>6943642</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8903,32 +8903,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127303436</v>
+        <v>127302751</v>
       </c>
       <c r="B75" t="n">
-        <v>75142</v>
+        <v>91906</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>760</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490658</v>
+        <v>490726</v>
       </c>
       <c r="R75" t="n">
-        <v>6943642</v>
+        <v>6943641</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9013,7 +9013,7 @@
         <v>127304100</v>
       </c>
       <c r="B76" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>127304206</v>
       </c>
       <c r="B77" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>127304672</v>
       </c>
       <c r="B78" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>127302585</v>
       </c>
       <c r="B79" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>127303834</v>
       </c>
       <c r="B80" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>127305164</v>
       </c>
       <c r="B81" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>127304951</v>
       </c>
       <c r="B82" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>127304399</v>
       </c>
       <c r="B83" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -8689,32 +8689,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127305232</v>
+        <v>127302751</v>
       </c>
       <c r="B73" t="n">
-        <v>79020</v>
+        <v>91906</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490703</v>
+        <v>490726</v>
       </c>
       <c r="R73" t="n">
-        <v>6943512</v>
+        <v>6943641</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8796,10 +8796,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127303436</v>
+        <v>127305232</v>
       </c>
       <c r="B74" t="n">
-        <v>75144</v>
+        <v>79020</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490658</v>
+        <v>490703</v>
       </c>
       <c r="R74" t="n">
-        <v>6943642</v>
+        <v>6943512</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8903,32 +8903,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127302751</v>
+        <v>127303436</v>
       </c>
       <c r="B75" t="n">
-        <v>91906</v>
+        <v>75144</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>760</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490726</v>
+        <v>490658</v>
       </c>
       <c r="R75" t="n">
-        <v>6943641</v>
+        <v>6943642</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY83"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8689,32 +8689,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127302751</v>
+        <v>127305232</v>
       </c>
       <c r="B73" t="n">
-        <v>91906</v>
+        <v>79020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490726</v>
+        <v>490703</v>
       </c>
       <c r="R73" t="n">
-        <v>6943641</v>
+        <v>6943512</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8796,10 +8796,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127305232</v>
+        <v>127303436</v>
       </c>
       <c r="B74" t="n">
-        <v>79020</v>
+        <v>75144</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490703</v>
+        <v>490658</v>
       </c>
       <c r="R74" t="n">
-        <v>6943512</v>
+        <v>6943642</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8903,32 +8903,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127303436</v>
+        <v>127302751</v>
       </c>
       <c r="B75" t="n">
-        <v>75144</v>
+        <v>91912</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>760</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490658</v>
+        <v>490726</v>
       </c>
       <c r="R75" t="n">
-        <v>6943642</v>
+        <v>6943641</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9660,7 +9660,7 @@
         <v>127304951</v>
       </c>
       <c r="B82" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>127304399</v>
       </c>
       <c r="B83" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9882,6 +9882,685 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127830128</v>
+      </c>
+      <c r="B84" t="n">
+        <v>58340</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>490736</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6943785</v>
+      </c>
+      <c r="S84" t="n">
+        <v>50</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Inspelad ett flertal gånger I augusti 2025</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>127830119</v>
+      </c>
+      <c r="B85" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>490736</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6943785</v>
+      </c>
+      <c r="S85" t="n">
+        <v>50</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Inspelad ett flertal gånger I augusti 2025</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127830123</v>
+      </c>
+      <c r="B86" t="n">
+        <v>58098</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>490736</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6943785</v>
+      </c>
+      <c r="S86" t="n">
+        <v>50</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Inspelad ett flertal gånger I augusti 2025</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127830118</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57313</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Smålom</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Gavia stellata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>490736</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6943785</v>
+      </c>
+      <c r="S87" t="n">
+        <v>50</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Läte inspelat, mest troligt under förbiflygning</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>127830121</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>490736</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6943785</v>
+      </c>
+      <c r="S88" t="n">
+        <v>50</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Inspelad ett flertal gånger I augusti 2025</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>127830103</v>
+      </c>
+      <c r="B89" t="n">
+        <v>58093</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Stor-Öravattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>490736</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6943785</v>
+      </c>
+      <c r="S89" t="n">
+        <v>50</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -8692,7 +8692,7 @@
         <v>127305232</v>
       </c>
       <c r="B73" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8796,32 +8796,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127303436</v>
+        <v>127302751</v>
       </c>
       <c r="B74" t="n">
-        <v>75144</v>
+        <v>91915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>760</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490658</v>
+        <v>490726</v>
       </c>
       <c r="R74" t="n">
-        <v>6943642</v>
+        <v>6943641</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8903,32 +8903,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127302751</v>
+        <v>127303436</v>
       </c>
       <c r="B75" t="n">
-        <v>91912</v>
+        <v>75147</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>760</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490726</v>
+        <v>490658</v>
       </c>
       <c r="R75" t="n">
-        <v>6943641</v>
+        <v>6943642</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9013,7 +9013,7 @@
         <v>127304100</v>
       </c>
       <c r="B76" t="n">
-        <v>80151</v>
+        <v>80154</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>127304206</v>
       </c>
       <c r="B77" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>127304672</v>
       </c>
       <c r="B78" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>127302585</v>
       </c>
       <c r="B79" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>127303834</v>
       </c>
       <c r="B80" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>127305164</v>
       </c>
       <c r="B81" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>127304951</v>
       </c>
       <c r="B82" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>127304399</v>
       </c>
       <c r="B83" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>127830128</v>
       </c>
       <c r="B84" t="n">
-        <v>58340</v>
+        <v>58343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>127830119</v>
       </c>
       <c r="B85" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>127830123</v>
       </c>
       <c r="B86" t="n">
-        <v>58098</v>
+        <v>58101</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10227,10 +10227,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127830118</v>
+        <v>127830103</v>
       </c>
       <c r="B87" t="n">
-        <v>57313</v>
+        <v>58096</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10238,21 +10238,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100063</v>
+        <v>103001</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10260,7 +10260,7 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -10304,17 +10304,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Läte inspelat, mest troligt under förbiflygning</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10344,7 +10339,7 @@
         <v>127830121</v>
       </c>
       <c r="B88" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10455,10 +10450,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127830103</v>
+        <v>127830118</v>
       </c>
       <c r="B89" t="n">
-        <v>58093</v>
+        <v>57316</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10466,21 +10461,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103001</v>
+        <v>100063</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10488,7 +10483,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -10532,12 +10527,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Läte inspelat, mest troligt under förbiflygning</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -8692,7 +8692,7 @@
         <v>127305232</v>
       </c>
       <c r="B73" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8796,32 +8796,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127302751</v>
+        <v>127303436</v>
       </c>
       <c r="B74" t="n">
-        <v>91915</v>
+        <v>75153</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>760</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490726</v>
+        <v>490658</v>
       </c>
       <c r="R74" t="n">
-        <v>6943641</v>
+        <v>6943642</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8903,32 +8903,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127303436</v>
+        <v>127302751</v>
       </c>
       <c r="B75" t="n">
-        <v>75147</v>
+        <v>91923</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>760</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490658</v>
+        <v>490726</v>
       </c>
       <c r="R75" t="n">
-        <v>6943642</v>
+        <v>6943641</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9013,7 +9013,7 @@
         <v>127304100</v>
       </c>
       <c r="B76" t="n">
-        <v>80154</v>
+        <v>80160</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>127304206</v>
       </c>
       <c r="B77" t="n">
-        <v>80127</v>
+        <v>80133</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>127304672</v>
       </c>
       <c r="B78" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>127302585</v>
       </c>
       <c r="B79" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>127303834</v>
       </c>
       <c r="B80" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>127305164</v>
       </c>
       <c r="B81" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>127304951</v>
       </c>
       <c r="B82" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>127304399</v>
       </c>
       <c r="B83" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>127830128</v>
       </c>
       <c r="B84" t="n">
-        <v>58343</v>
+        <v>58349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>127830119</v>
       </c>
       <c r="B85" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>127830123</v>
       </c>
       <c r="B86" t="n">
-        <v>58101</v>
+        <v>58107</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10227,10 +10227,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127830103</v>
+        <v>127830118</v>
       </c>
       <c r="B87" t="n">
-        <v>58096</v>
+        <v>57322</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10238,21 +10238,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103001</v>
+        <v>100063</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10260,7 +10260,7 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -10304,12 +10304,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Läte inspelat, mest troligt under förbiflygning</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10336,10 +10341,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127830121</v>
+        <v>127830103</v>
       </c>
       <c r="B88" t="n">
-        <v>57826</v>
+        <v>58102</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10347,21 +10352,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10413,17 +10418,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Inspelad ett flertal gånger I augusti 2025</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10450,10 +10450,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127830118</v>
+        <v>127830121</v>
       </c>
       <c r="B89" t="n">
-        <v>57316</v>
+        <v>57832</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10461,21 +10461,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100063</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10483,7 +10483,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -10527,17 +10527,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Läte inspelat, mest troligt under förbiflygning</t>
+          <t>Inspelad ett flertal gånger I augusti 2025</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -8689,32 +8689,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127305232</v>
+        <v>127302751</v>
       </c>
       <c r="B73" t="n">
-        <v>79029</v>
+        <v>91924</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490703</v>
+        <v>490726</v>
       </c>
       <c r="R73" t="n">
-        <v>6943512</v>
+        <v>6943641</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8796,10 +8796,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127303436</v>
+        <v>127305232</v>
       </c>
       <c r="B74" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490658</v>
+        <v>490703</v>
       </c>
       <c r="R74" t="n">
-        <v>6943642</v>
+        <v>6943512</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8903,32 +8903,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127302751</v>
+        <v>127303436</v>
       </c>
       <c r="B75" t="n">
-        <v>91923</v>
+        <v>75153</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>760</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490726</v>
+        <v>490658</v>
       </c>
       <c r="R75" t="n">
-        <v>6943641</v>
+        <v>6943642</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9660,7 +9660,7 @@
         <v>127304951</v>
       </c>
       <c r="B82" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>127304399</v>
       </c>
       <c r="B83" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10341,10 +10341,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127830103</v>
+        <v>127830121</v>
       </c>
       <c r="B88" t="n">
-        <v>58102</v>
+        <v>57832</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10352,21 +10352,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10418,12 +10418,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Inspelad ett flertal gånger I augusti 2025</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10450,10 +10455,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127830121</v>
+        <v>127830103</v>
       </c>
       <c r="B89" t="n">
-        <v>57832</v>
+        <v>58102</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10461,21 +10466,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10527,17 +10532,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Inspelad ett flertal gånger I augusti 2025</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -8689,32 +8689,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127302751</v>
+        <v>127303436</v>
       </c>
       <c r="B73" t="n">
-        <v>91924</v>
+        <v>75153</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>760</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490726</v>
+        <v>490658</v>
       </c>
       <c r="R73" t="n">
-        <v>6943641</v>
+        <v>6943642</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8796,32 +8796,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127305232</v>
+        <v>127302751</v>
       </c>
       <c r="B74" t="n">
-        <v>79029</v>
+        <v>91924</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490703</v>
+        <v>490726</v>
       </c>
       <c r="R74" t="n">
-        <v>6943512</v>
+        <v>6943641</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8903,10 +8903,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127303436</v>
+        <v>127305232</v>
       </c>
       <c r="B75" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8914,21 +8914,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490658</v>
+        <v>490703</v>
       </c>
       <c r="R75" t="n">
-        <v>6943642</v>
+        <v>6943512</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10227,10 +10227,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127830118</v>
+        <v>127830103</v>
       </c>
       <c r="B87" t="n">
-        <v>57322</v>
+        <v>58102</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10238,21 +10238,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100063</v>
+        <v>103001</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10260,7 +10260,7 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -10304,17 +10304,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Läte inspelat, mest troligt under förbiflygning</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10455,10 +10450,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127830103</v>
+        <v>127830118</v>
       </c>
       <c r="B89" t="n">
-        <v>58102</v>
+        <v>57322</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10466,21 +10461,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103001</v>
+        <v>100063</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10488,7 +10483,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -10532,12 +10527,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Läte inspelat, mest troligt under förbiflygning</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -8689,10 +8689,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127303436</v>
+        <v>127305232</v>
       </c>
       <c r="B73" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8700,21 +8700,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490658</v>
+        <v>490703</v>
       </c>
       <c r="R73" t="n">
-        <v>6943642</v>
+        <v>6943512</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8796,32 +8796,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127302751</v>
+        <v>127303436</v>
       </c>
       <c r="B74" t="n">
-        <v>91924</v>
+        <v>75153</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>760</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490726</v>
+        <v>490658</v>
       </c>
       <c r="R74" t="n">
-        <v>6943641</v>
+        <v>6943642</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8903,32 +8903,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127305232</v>
+        <v>127302751</v>
       </c>
       <c r="B75" t="n">
-        <v>79029</v>
+        <v>91925</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490703</v>
+        <v>490726</v>
       </c>
       <c r="R75" t="n">
-        <v>6943512</v>
+        <v>6943641</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9660,7 +9660,7 @@
         <v>127304951</v>
       </c>
       <c r="B82" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>127304399</v>
       </c>
       <c r="B83" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10227,10 +10227,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127830103</v>
+        <v>127830118</v>
       </c>
       <c r="B87" t="n">
-        <v>58102</v>
+        <v>57322</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10238,21 +10238,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103001</v>
+        <v>100063</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10260,7 +10260,7 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -10304,12 +10304,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Läte inspelat, mest troligt under förbiflygning</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10336,10 +10341,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127830121</v>
+        <v>127830103</v>
       </c>
       <c r="B88" t="n">
-        <v>57832</v>
+        <v>58102</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10347,21 +10352,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10413,17 +10418,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Inspelad ett flertal gånger I augusti 2025</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10450,10 +10450,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127830118</v>
+        <v>127830121</v>
       </c>
       <c r="B89" t="n">
-        <v>57322</v>
+        <v>57832</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10461,21 +10461,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100063</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10483,7 +10483,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -10527,17 +10527,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Läte inspelat, mest troligt under förbiflygning</t>
+          <t>Inspelad ett flertal gånger I augusti 2025</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -10341,10 +10341,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127830103</v>
+        <v>127830121</v>
       </c>
       <c r="B88" t="n">
-        <v>58102</v>
+        <v>57832</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10352,21 +10352,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10418,12 +10418,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Inspelad ett flertal gånger I augusti 2025</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10450,10 +10455,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127830121</v>
+        <v>127830103</v>
       </c>
       <c r="B89" t="n">
-        <v>57832</v>
+        <v>58102</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10461,21 +10466,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10527,17 +10532,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Inspelad ett flertal gånger I augusti 2025</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -9888,7 +9888,7 @@
         <v>127830128</v>
       </c>
       <c r="B84" t="n">
-        <v>58349</v>
+        <v>58350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>127830119</v>
       </c>
       <c r="B85" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>127830123</v>
       </c>
       <c r="B86" t="n">
-        <v>58107</v>
+        <v>58108</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10341,10 +10341,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127830121</v>
+        <v>127830103</v>
       </c>
       <c r="B88" t="n">
-        <v>57832</v>
+        <v>58103</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10352,21 +10352,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10418,17 +10418,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Inspelad ett flertal gånger I augusti 2025</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10455,10 +10450,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127830103</v>
+        <v>127830121</v>
       </c>
       <c r="B89" t="n">
-        <v>58102</v>
+        <v>57833</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10466,21 +10461,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10532,12 +10527,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Inspelad ett flertal gånger I augusti 2025</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -9888,7 +9888,7 @@
         <v>127830128</v>
       </c>
       <c r="B84" t="n">
-        <v>58350</v>
+        <v>58362</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>127830119</v>
       </c>
       <c r="B85" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>127830123</v>
       </c>
       <c r="B86" t="n">
-        <v>58108</v>
+        <v>58120</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10227,10 +10227,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127830118</v>
+        <v>127830103</v>
       </c>
       <c r="B87" t="n">
-        <v>57322</v>
+        <v>58115</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10238,21 +10238,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100063</v>
+        <v>103001</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10260,7 +10260,7 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -10304,17 +10304,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Läte inspelat, mest troligt under förbiflygning</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10341,10 +10336,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127830103</v>
+        <v>127830121</v>
       </c>
       <c r="B88" t="n">
-        <v>58103</v>
+        <v>57845</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10352,21 +10347,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10418,12 +10413,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Inspelad ett flertal gånger I augusti 2025</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10450,10 +10450,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127830121</v>
+        <v>127830118</v>
       </c>
       <c r="B89" t="n">
-        <v>57833</v>
+        <v>57334</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10461,21 +10461,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>100063</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10483,7 +10483,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -10527,17 +10527,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Inspelad ett flertal gånger I augusti 2025</t>
+          <t>Läte inspelat, mest troligt under förbiflygning</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -10227,10 +10227,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127830103</v>
+        <v>127830118</v>
       </c>
       <c r="B87" t="n">
-        <v>58115</v>
+        <v>57334</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10238,21 +10238,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103001</v>
+        <v>100063</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10260,7 +10260,7 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -10304,12 +10304,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Läte inspelat, mest troligt under förbiflygning</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10450,10 +10455,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127830118</v>
+        <v>127830103</v>
       </c>
       <c r="B89" t="n">
-        <v>57334</v>
+        <v>58115</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10461,21 +10466,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100063</v>
+        <v>103001</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10483,7 +10488,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -10527,17 +10532,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Läte inspelat, mest troligt under förbiflygning</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -10227,10 +10227,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127830118</v>
+        <v>127830103</v>
       </c>
       <c r="B87" t="n">
-        <v>57334</v>
+        <v>58115</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10238,21 +10238,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100063</v>
+        <v>103001</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10260,7 +10260,7 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -10304,17 +10304,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Läte inspelat, mest troligt under förbiflygning</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10455,10 +10450,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127830103</v>
+        <v>127830118</v>
       </c>
       <c r="B89" t="n">
-        <v>58115</v>
+        <v>57334</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10466,21 +10461,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103001</v>
+        <v>100063</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10488,7 +10483,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -10532,12 +10527,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Läte inspelat, mest troligt under förbiflygning</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -10227,10 +10227,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127830103</v>
+        <v>127830118</v>
       </c>
       <c r="B87" t="n">
-        <v>58115</v>
+        <v>57334</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10238,21 +10238,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103001</v>
+        <v>100063</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10260,7 +10260,7 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -10304,12 +10304,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Läte inspelat, mest troligt under förbiflygning</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10336,10 +10341,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127830121</v>
+        <v>127830103</v>
       </c>
       <c r="B88" t="n">
-        <v>57845</v>
+        <v>58115</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10347,21 +10352,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10413,17 +10418,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Inspelad ett flertal gånger I augusti 2025</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10450,10 +10450,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127830118</v>
+        <v>127830121</v>
       </c>
       <c r="B89" t="n">
-        <v>57334</v>
+        <v>57845</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10461,21 +10461,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100063</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10483,7 +10483,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -10527,17 +10527,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Läte inspelat, mest troligt under förbiflygning</t>
+          <t>Inspelad ett flertal gånger I augusti 2025</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -8689,32 +8689,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127305232</v>
+        <v>127302751</v>
       </c>
       <c r="B73" t="n">
-        <v>79029</v>
+        <v>91893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490703</v>
+        <v>490726</v>
       </c>
       <c r="R73" t="n">
-        <v>6943512</v>
+        <v>6943641</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8799,7 +8799,7 @@
         <v>127303436</v>
       </c>
       <c r="B74" t="n">
-        <v>75153</v>
+        <v>75135</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8903,32 +8903,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127302751</v>
+        <v>127305232</v>
       </c>
       <c r="B75" t="n">
-        <v>91925</v>
+        <v>79011</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490726</v>
+        <v>490703</v>
       </c>
       <c r="R75" t="n">
-        <v>6943641</v>
+        <v>6943512</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9013,7 +9013,7 @@
         <v>127304100</v>
       </c>
       <c r="B76" t="n">
-        <v>80160</v>
+        <v>80142</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>127304206</v>
       </c>
       <c r="B77" t="n">
-        <v>80133</v>
+        <v>80115</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>127304672</v>
       </c>
       <c r="B78" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>127302585</v>
       </c>
       <c r="B79" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>127303834</v>
       </c>
       <c r="B80" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>127305164</v>
       </c>
       <c r="B81" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>127304951</v>
       </c>
       <c r="B82" t="n">
-        <v>98469</v>
+        <v>98436</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>127304399</v>
       </c>
       <c r="B83" t="n">
-        <v>97346</v>
+        <v>97314</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117159903</v>
+        <v>119567445</v>
       </c>
       <c r="B2" t="n">
-        <v>79525</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilltjärnen (Lilltjärnen), Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490717</v>
+        <v>490638</v>
       </c>
       <c r="R2" t="n">
-        <v>6943648</v>
+        <v>6943512</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119569970</v>
+        <v>119604751</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490505</v>
+        <v>490670</v>
       </c>
       <c r="R3" t="n">
-        <v>6943750</v>
+        <v>6943745</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -857,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119562658</v>
+        <v>119611969</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +900,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490654</v>
+        <v>490646</v>
       </c>
       <c r="R4" t="n">
-        <v>6943443</v>
+        <v>6943773</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,6 +972,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,53 +991,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119565821</v>
+        <v>127302751</v>
       </c>
       <c r="B5" t="n">
-        <v>74638</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490631</v>
+        <v>490726</v>
       </c>
       <c r="R5" t="n">
-        <v>6943382</v>
+        <v>6943641</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1056,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119573937</v>
+        <v>119561285</v>
       </c>
       <c r="B6" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,40 +1109,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490506</v>
+        <v>490846</v>
       </c>
       <c r="R6" t="n">
-        <v>6943700</v>
+        <v>6943525</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,18 +1166,27 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1229,50 +1205,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119566746</v>
+        <v>119560972</v>
       </c>
       <c r="B7" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490599</v>
+        <v>490865</v>
       </c>
       <c r="R7" t="n">
-        <v>6943415</v>
+        <v>6943527</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1304,7 +1275,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1285,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,53 +1312,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119561285</v>
+        <v>119573937</v>
       </c>
       <c r="B8" t="n">
-        <v>90558</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490846</v>
+        <v>490506</v>
       </c>
       <c r="R8" t="n">
-        <v>6943525</v>
+        <v>6943700</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1414,27 +1383,18 @@
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1453,53 +1413,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119565471</v>
+        <v>119611930</v>
       </c>
       <c r="B9" t="n">
-        <v>74638</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490635</v>
+        <v>490703</v>
       </c>
       <c r="R9" t="n">
-        <v>6943355</v>
+        <v>6943806</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,27 +1481,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Många mycket gamla granar längs sjön</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,6 +1495,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1570,50 +1514,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119567326</v>
+        <v>119564989</v>
       </c>
       <c r="B10" t="n">
-        <v>79635</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490636</v>
+        <v>490648</v>
       </c>
       <c r="R10" t="n">
-        <v>6943499</v>
+        <v>6943345</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1645,7 +1584,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,7 +1594,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Många mycket gamla granar längs stranden</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,15 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119562305</v>
+        <v>119566746</v>
       </c>
       <c r="B11" t="n">
-        <v>79115</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,34 +1637,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490757</v>
+        <v>490599</v>
       </c>
       <c r="R11" t="n">
-        <v>6943439</v>
+        <v>6943415</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1757,7 +1696,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1767,7 +1706,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,59 +1733,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119563399</v>
+        <v>119599421</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490675</v>
+        <v>490822</v>
       </c>
       <c r="R12" t="n">
-        <v>6943404</v>
+        <v>6943695</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1873,22 +1798,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,15 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119567978</v>
+        <v>119600343</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,34 +1851,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490638</v>
+        <v>490740</v>
       </c>
       <c r="R13" t="n">
-        <v>6943600</v>
+        <v>6943762</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1985,22 +1905,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,15 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119561375</v>
+        <v>119602140</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,34 +1958,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490834</v>
+        <v>490645</v>
       </c>
       <c r="R14" t="n">
-        <v>6943520</v>
+        <v>6943768</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2097,22 +2012,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,15 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119570160</v>
+        <v>127304206</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,37 +2065,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490561</v>
+        <v>490622</v>
       </c>
       <c r="R15" t="n">
-        <v>6943765</v>
+        <v>6943589</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2209,22 +2119,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,19 +2161,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119570901</v>
+        <v>119560369</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2291,13 +2196,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490713</v>
+        <v>490931</v>
       </c>
       <c r="R16" t="n">
-        <v>6943822</v>
+        <v>6943570</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2326,7 +2231,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2336,7 +2241,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,15 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119568797</v>
+        <v>119561375</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,43 +2279,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490501</v>
+        <v>490834</v>
       </c>
       <c r="R17" t="n">
-        <v>6943638</v>
+        <v>6943520</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2447,7 +2338,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2457,7 +2348,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,37 +2375,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119567445</v>
+        <v>119562658</v>
       </c>
       <c r="B18" t="n">
-        <v>95455</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2524,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490638</v>
+        <v>490654</v>
       </c>
       <c r="R18" t="n">
-        <v>6943512</v>
+        <v>6943443</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2559,7 +2445,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2569,7 +2455,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2596,50 +2482,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119568960</v>
+        <v>119565707</v>
       </c>
       <c r="B19" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490488</v>
+        <v>490616</v>
       </c>
       <c r="R19" t="n">
-        <v>6943660</v>
+        <v>6943373</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2671,7 +2552,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2681,7 +2562,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,19 +2589,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119570334</v>
+        <v>119566845</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2744,14 +2620,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490582</v>
+        <v>490615</v>
       </c>
       <c r="R20" t="n">
-        <v>6943798</v>
+        <v>6943447</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2783,7 +2659,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2793,7 +2669,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2820,50 +2696,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119568892</v>
+        <v>119567943</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490488</v>
+        <v>490651</v>
       </c>
       <c r="R21" t="n">
-        <v>6943660</v>
+        <v>6943582</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2895,7 +2766,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2905,12 +2776,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På stor asp</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2937,37 +2803,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119570777</v>
+        <v>119570334</v>
       </c>
       <c r="B22" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2977,10 +2838,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490693</v>
+        <v>490582</v>
       </c>
       <c r="R22" t="n">
-        <v>6943819</v>
+        <v>6943798</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3012,7 +2873,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3022,7 +2883,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3049,19 +2910,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119565707</v>
+        <v>119570901</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3085,14 +2941,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490616</v>
+        <v>490713</v>
       </c>
       <c r="R23" t="n">
-        <v>6943373</v>
+        <v>6943822</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3124,7 +2980,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3134,7 +2990,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,50 +3017,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119567047</v>
+        <v>119598830</v>
       </c>
       <c r="B24" t="n">
-        <v>74638</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490615</v>
+        <v>490809</v>
       </c>
       <c r="R24" t="n">
-        <v>6943448</v>
+        <v>6943632</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3231,22 +3082,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3273,50 +3124,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119570068</v>
+        <v>119599504</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490537</v>
+        <v>490789</v>
       </c>
       <c r="R25" t="n">
-        <v>6943742</v>
+        <v>6943691</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3343,22 +3189,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3385,50 +3231,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119567265</v>
+        <v>119603478</v>
       </c>
       <c r="B26" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490622</v>
+        <v>490638</v>
       </c>
       <c r="R26" t="n">
-        <v>6943503</v>
+        <v>6943741</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3455,22 +3296,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3497,53 +3338,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119564989</v>
+        <v>127302585</v>
       </c>
       <c r="B27" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490648</v>
+        <v>490729</v>
       </c>
       <c r="R27" t="n">
-        <v>6943345</v>
+        <v>6943626</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3567,27 +3403,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Många mycket gamla granar längs stranden</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3614,53 +3445,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119567682</v>
+        <v>127305232</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490645</v>
+        <v>490703</v>
       </c>
       <c r="R28" t="n">
-        <v>6943575</v>
+        <v>6943512</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3684,27 +3510,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Vid surhål /kallkälla</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3731,59 +3552,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119569847</v>
+        <v>119565471</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490462</v>
+        <v>490635</v>
       </c>
       <c r="R29" t="n">
-        <v>6943718</v>
+        <v>6943355</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3815,7 +3622,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3825,7 +3632,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Många mycket gamla granar längs sjön</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3852,59 +3664,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119569440</v>
+        <v>119565821</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490493</v>
+        <v>490631</v>
       </c>
       <c r="R30" t="n">
-        <v>6943708</v>
+        <v>6943382</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3936,7 +3734,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3946,7 +3744,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3973,15 +3771,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119566845</v>
+        <v>119566592</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3989,34 +3782,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490615</v>
+        <v>490606</v>
       </c>
       <c r="R31" t="n">
-        <v>6943447</v>
+        <v>6943414</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4048,7 +3841,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4058,7 +3851,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4085,59 +3878,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119569122</v>
+        <v>119567047</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490488</v>
+        <v>490615</v>
       </c>
       <c r="R32" t="n">
-        <v>6943685</v>
+        <v>6943448</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4169,7 +3948,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4179,7 +3958,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4206,59 +3985,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119568632</v>
+        <v>119598641</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Öravattskojan, Öravattskojan, Jmt</t>
+          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490519</v>
+        <v>490892</v>
       </c>
       <c r="R33" t="n">
-        <v>6943605</v>
+        <v>6943588</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4285,22 +4050,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4327,15 +4092,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119560972</v>
+        <v>119599288</v>
       </c>
       <c r="B34" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4343,34 +4103,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490865</v>
+        <v>490822</v>
       </c>
       <c r="R34" t="n">
-        <v>6943527</v>
+        <v>6943695</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4397,22 +4157,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4439,15 +4199,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119567943</v>
+        <v>119605333</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4455,34 +4210,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490651</v>
+        <v>490655</v>
       </c>
       <c r="R35" t="n">
-        <v>6943582</v>
+        <v>6943683</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4509,22 +4264,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4551,15 +4306,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119560369</v>
+        <v>119611984</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4567,34 +4317,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490931</v>
+        <v>490643</v>
       </c>
       <c r="R36" t="n">
-        <v>6943570</v>
+        <v>6943759</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4621,22 +4374,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4645,6 +4388,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4663,15 +4407,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119562537</v>
+        <v>127303436</v>
       </c>
       <c r="B37" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4679,42 +4418,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490683</v>
+        <v>490658</v>
       </c>
       <c r="R37" t="n">
-        <v>6943465</v>
+        <v>6943642</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4738,22 +4472,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4780,15 +4514,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119566592</v>
+        <v>117159903</v>
       </c>
       <c r="B38" t="n">
-        <v>74638</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4796,37 +4525,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490606</v>
+        <v>490717</v>
       </c>
       <c r="R38" t="n">
-        <v>6943414</v>
+        <v>6943648</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4850,22 +4579,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4880,27 +4609,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119570243</v>
+        <v>119567682</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4928,14 +4652,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490559</v>
+        <v>490645</v>
       </c>
       <c r="R39" t="n">
-        <v>6943786</v>
+        <v>6943575</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4967,7 +4691,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4977,7 +4701,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Vid surhål /kallkälla</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5004,62 +4733,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119570130</v>
+        <v>119567978</v>
       </c>
       <c r="B40" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490580</v>
+        <v>490638</v>
       </c>
       <c r="R40" t="n">
-        <v>6943769</v>
+        <v>6943600</v>
       </c>
       <c r="S40" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5088,7 +4803,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5098,7 +4813,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5125,15 +4840,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119611930</v>
+        <v>119568892</v>
       </c>
       <c r="B41" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5141,40 +4851,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490703</v>
+        <v>490488</v>
       </c>
       <c r="R41" t="n">
-        <v>6943806</v>
+        <v>6943660</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5198,12 +4905,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På stor asp</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5212,7 +4934,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5231,15 +4952,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119604081</v>
+        <v>119569970</v>
       </c>
       <c r="B42" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5267,14 +4983,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490614</v>
+        <v>490505</v>
       </c>
       <c r="R42" t="n">
-        <v>6943732</v>
+        <v>6943750</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5301,22 +5017,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5343,15 +5059,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119612016</v>
+        <v>119570068</v>
       </c>
       <c r="B43" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5377,22 +5088,19 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490631</v>
+        <v>490537</v>
       </c>
       <c r="R43" t="n">
         <v>6943742</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5416,12 +5124,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5430,7 +5148,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5449,15 +5166,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119603478</v>
+        <v>119570160</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5465,34 +5177,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490638</v>
+        <v>490561</v>
       </c>
       <c r="R44" t="n">
-        <v>6943741</v>
+        <v>6943765</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5519,22 +5231,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5561,15 +5273,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119611984</v>
+        <v>119570243</v>
       </c>
       <c r="B45" t="n">
-        <v>74638</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5577,40 +5284,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490643</v>
+        <v>490559</v>
       </c>
       <c r="R45" t="n">
-        <v>6943759</v>
+        <v>6943786</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5634,12 +5338,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5648,7 +5362,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5667,15 +5380,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119602140</v>
+        <v>119570777</v>
       </c>
       <c r="B46" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5683,34 +5391,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490645</v>
+        <v>490693</v>
       </c>
       <c r="R46" t="n">
-        <v>6943768</v>
+        <v>6943819</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5737,22 +5445,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5779,57 +5487,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119611906</v>
+        <v>119598920</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490727</v>
+        <v>490801</v>
       </c>
       <c r="R47" t="n">
-        <v>6943794</v>
+        <v>6943688</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5856,18 +5555,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5886,57 +5594,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119611914</v>
+        <v>119603962</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490694</v>
+        <v>490609</v>
       </c>
       <c r="R48" t="n">
-        <v>6943829</v>
+        <v>6943775</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5963,18 +5662,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5993,15 +5701,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119599641</v>
+        <v>119604081</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6009,39 +5712,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490793</v>
+        <v>490614</v>
       </c>
       <c r="R49" t="n">
-        <v>6943720</v>
+        <v>6943732</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6073,7 +5771,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6083,7 +5781,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6110,15 +5808,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119599288</v>
+        <v>119605869</v>
       </c>
       <c r="B50" t="n">
-        <v>74638</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6126,21 +5819,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6150,10 +5843,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490822</v>
+        <v>490678</v>
       </c>
       <c r="R50" t="n">
-        <v>6943695</v>
+        <v>6943630</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6185,7 +5878,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6195,7 +5888,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6222,15 +5915,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119611969</v>
+        <v>119611689</v>
       </c>
       <c r="B51" t="n">
-        <v>95455</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6238,27 +5926,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6266,13 +5953,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490646</v>
+        <v>490801</v>
       </c>
       <c r="R51" t="n">
-        <v>6943773</v>
+        <v>6943720</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6329,51 +6016,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119611864</v>
+        <v>119612016</v>
       </c>
       <c r="B52" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6381,10 +6054,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490760</v>
+        <v>490631</v>
       </c>
       <c r="R52" t="n">
-        <v>6943743</v>
+        <v>6943742</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6444,15 +6117,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119598830</v>
+        <v>127303834</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6460,21 +6128,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6484,13 +6152,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490809</v>
+        <v>490619</v>
       </c>
       <c r="R53" t="n">
-        <v>6943632</v>
+        <v>6943643</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6514,22 +6182,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På död stående sälg med bohål och födospår från hackspett</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6556,37 +6229,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119603940</v>
+        <v>127304672</v>
       </c>
       <c r="B54" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6596,13 +6264,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490609</v>
+        <v>490643</v>
       </c>
       <c r="R54" t="n">
-        <v>6943769</v>
+        <v>6943554</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6626,22 +6294,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6668,15 +6336,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119603962</v>
+        <v>127305164</v>
       </c>
       <c r="B55" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6708,13 +6371,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490609</v>
+        <v>490690</v>
       </c>
       <c r="R55" t="n">
-        <v>6943775</v>
+        <v>6943499</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6738,22 +6401,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6780,50 +6443,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119600343</v>
+        <v>119567326</v>
       </c>
       <c r="B56" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490740</v>
+        <v>490636</v>
       </c>
       <c r="R56" t="n">
-        <v>6943762</v>
+        <v>6943499</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6850,22 +6508,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6892,58 +6550,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119612354</v>
+        <v>127304100</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490610</v>
+        <v>490611</v>
       </c>
       <c r="R57" t="n">
-        <v>6943724</v>
+        <v>6943604</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6970,17 +6615,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7007,50 +6657,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119602492</v>
+        <v>119567265</v>
       </c>
       <c r="B58" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490621</v>
+        <v>490622</v>
       </c>
       <c r="R58" t="n">
-        <v>6943759</v>
+        <v>6943503</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7077,22 +6722,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7119,53 +6764,51 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119598920</v>
+        <v>119612059</v>
       </c>
       <c r="B59" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490801</v>
+        <v>490631</v>
       </c>
       <c r="R59" t="n">
-        <v>6943688</v>
+        <v>6943742</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7192,27 +6835,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7231,50 +6865,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119605869</v>
+        <v>119568960</v>
       </c>
       <c r="B60" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490678</v>
+        <v>490488</v>
       </c>
       <c r="R60" t="n">
-        <v>6943630</v>
+        <v>6943660</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7301,22 +6930,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7343,65 +6972,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119612090</v>
+        <v>119603940</v>
       </c>
       <c r="B61" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490631</v>
+        <v>490609</v>
       </c>
       <c r="R61" t="n">
-        <v>6943742</v>
+        <v>6943769</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7428,18 +7040,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7458,65 +7079,60 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119611950</v>
+        <v>127830118</v>
       </c>
       <c r="B62" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57602</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100063</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490710</v>
+        <v>490736</v>
       </c>
       <c r="R62" t="n">
-        <v>6943807</v>
+        <v>6943785</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7540,12 +7156,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Läte inspelat, mest troligt under förbiflygning</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7554,7 +7175,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7573,65 +7193,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119611850</v>
+        <v>119599641</v>
       </c>
       <c r="B63" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490774</v>
+        <v>490793</v>
       </c>
       <c r="R63" t="n">
-        <v>6943748</v>
+        <v>6943720</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7658,18 +7266,27 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7688,15 +7305,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119599421</v>
+        <v>119612354</v>
       </c>
       <c r="B64" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7704,37 +7316,45 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490822</v>
+        <v>490610</v>
       </c>
       <c r="R64" t="n">
-        <v>6943695</v>
+        <v>6943724</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7761,19 +7381,14 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7800,53 +7415,57 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119599504</v>
+        <v>119570130</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lill-Öravattnet, Lill-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490789</v>
+        <v>490580</v>
       </c>
       <c r="R65" t="n">
-        <v>6943691</v>
+        <v>6943769</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7870,22 +7489,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7915,12 +7534,7 @@
         <v>119605344</v>
       </c>
       <c r="B66" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8029,15 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119598641</v>
+        <v>127830123</v>
       </c>
       <c r="B67" t="n">
-        <v>74638</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8045,37 +7654,49 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>102999</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lilltjärnmyren, Lilltjärnmyren, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490892</v>
+        <v>490736</v>
       </c>
       <c r="R67" t="n">
-        <v>6943588</v>
+        <v>6943785</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8099,22 +7720,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Inspelad ett flertal gånger I augusti 2025</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8141,15 +7757,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119601996</v>
+        <v>127830103</v>
       </c>
       <c r="B68" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8157,37 +7768,49 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>103001</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490657</v>
+        <v>490736</v>
       </c>
       <c r="R68" t="n">
-        <v>6943791</v>
+        <v>6943785</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8211,22 +7834,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8253,15 +7866,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119612059</v>
+        <v>127830119</v>
       </c>
       <c r="B69" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8269,40 +7877,49 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>103015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490631</v>
+        <v>490736</v>
       </c>
       <c r="R69" t="n">
-        <v>6943742</v>
+        <v>6943785</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8326,12 +7943,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Inspelad ett flertal gånger I augusti 2025</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8340,7 +7962,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8359,15 +7980,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119605333</v>
+        <v>119562537</v>
       </c>
       <c r="B70" t="n">
-        <v>74638</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8375,37 +7991,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490655</v>
+        <v>490683</v>
       </c>
       <c r="R70" t="n">
-        <v>6943683</v>
+        <v>6943465</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8429,22 +8050,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8471,15 +8092,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119611689</v>
+        <v>127830121</v>
       </c>
       <c r="B71" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8487,40 +8103,49 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Storöravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490801</v>
+        <v>490736</v>
       </c>
       <c r="R71" t="n">
-        <v>6943720</v>
+        <v>6943785</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8544,12 +8169,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Inspelad ett flertal gånger I augusti 2025</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8558,7 +8188,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8577,53 +8206,60 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119604751</v>
+        <v>127830128</v>
       </c>
       <c r="B72" t="n">
-        <v>95478</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>103044</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490670</v>
+        <v>490736</v>
       </c>
       <c r="R72" t="n">
-        <v>6943745</v>
+        <v>6943785</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8647,22 +8283,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>16:23</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>16:23</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Inspelad ett flertal gånger I augusti 2025</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8689,48 +8320,57 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127305232</v>
+        <v>119563399</v>
       </c>
       <c r="B73" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490703</v>
+        <v>490675</v>
       </c>
       <c r="R73" t="n">
-        <v>6943512</v>
+        <v>6943404</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8754,22 +8394,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8796,48 +8436,57 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127303436</v>
+        <v>119568632</v>
       </c>
       <c r="B74" t="n">
-        <v>75153</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490658</v>
+        <v>490519</v>
       </c>
       <c r="R74" t="n">
-        <v>6943642</v>
+        <v>6943605</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8861,22 +8510,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8903,10 +8552,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127302751</v>
+        <v>119568797</v>
       </c>
       <c r="B75" t="n">
-        <v>91925</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8914,37 +8563,46 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490726</v>
+        <v>490501</v>
       </c>
       <c r="R75" t="n">
-        <v>6943641</v>
+        <v>6943638</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8968,22 +8626,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9010,48 +8668,57 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127304100</v>
+        <v>119569122</v>
       </c>
       <c r="B76" t="n">
-        <v>80160</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490611</v>
+        <v>490488</v>
       </c>
       <c r="R76" t="n">
-        <v>6943604</v>
+        <v>6943685</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9075,22 +8742,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9117,48 +8784,57 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127304206</v>
+        <v>119569440</v>
       </c>
       <c r="B77" t="n">
-        <v>80133</v>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490622</v>
+        <v>490493</v>
       </c>
       <c r="R77" t="n">
-        <v>6943589</v>
+        <v>6943708</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9182,22 +8858,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9224,48 +8900,57 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127304672</v>
+        <v>119569847</v>
       </c>
       <c r="B78" t="n">
-        <v>80132</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Öravattskojan, Öravattskojan, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>490643</v>
+        <v>490462</v>
       </c>
       <c r="R78" t="n">
-        <v>6943554</v>
+        <v>6943718</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9289,22 +8974,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9331,48 +9016,60 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127302585</v>
+        <v>119611850</v>
       </c>
       <c r="B79" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>490729</v>
+        <v>490774</v>
       </c>
       <c r="R79" t="n">
-        <v>6943626</v>
+        <v>6943748</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9396,22 +9093,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>20:09</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>20:09</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9420,6 +9107,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9438,45 +9126,57 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127303834</v>
+        <v>119611864</v>
       </c>
       <c r="B80" t="n">
-        <v>80132</v>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>490619</v>
+        <v>490760</v>
       </c>
       <c r="R80" t="n">
-        <v>6943643</v>
+        <v>6943743</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9503,27 +9203,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>20:35</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På död stående sälg med bohål och födospår från hackspett</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9532,6 +9217,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9550,45 +9236,49 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127305164</v>
+        <v>119611906</v>
       </c>
       <c r="B81" t="n">
-        <v>80132</v>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490690</v>
+        <v>490727</v>
       </c>
       <c r="R81" t="n">
-        <v>6943499</v>
+        <v>6943794</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9615,22 +9305,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>21:24</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>21:24</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9639,6 +9319,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9657,10 +9338,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127304951</v>
+        <v>119611914</v>
       </c>
       <c r="B82" t="n">
-        <v>98469</v>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9685,26 +9366,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490646</v>
+        <v>490694</v>
       </c>
       <c r="R82" t="n">
-        <v>6943520</v>
+        <v>6943829</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9731,22 +9407,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>21:14</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>21:14</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9755,6 +9421,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9773,45 +9440,57 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127304399</v>
+        <v>119611950</v>
       </c>
       <c r="B83" t="n">
-        <v>97346</v>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Storöravattnet, Storöravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490621</v>
+        <v>490710</v>
       </c>
       <c r="R83" t="n">
-        <v>6943586</v>
+        <v>6943807</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9838,27 +9517,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>20:59</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>20:59</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Vid litet surdråg</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9867,6 +9531,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9885,60 +9550,60 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127830128</v>
+        <v>119612090</v>
       </c>
       <c r="B84" t="n">
-        <v>58362</v>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490736</v>
+        <v>490631</v>
       </c>
       <c r="R84" t="n">
-        <v>6943785</v>
+        <v>6943742</v>
       </c>
       <c r="S84" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9962,17 +9627,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Inspelad ett flertal gånger I augusti 2025</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9981,6 +9641,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9999,60 +9660,57 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127830119</v>
+        <v>127304951</v>
       </c>
       <c r="B85" t="n">
-        <v>58055</v>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490736</v>
+        <v>490646</v>
       </c>
       <c r="R85" t="n">
-        <v>6943785</v>
+        <v>6943520</v>
       </c>
       <c r="S85" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10076,17 +9734,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Inspelad ett flertal gånger I augusti 2025</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10113,60 +9776,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127830123</v>
+        <v>127304399</v>
       </c>
       <c r="B86" t="n">
-        <v>58120</v>
+        <v>97983</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>102999</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>490736</v>
+        <v>490621</v>
       </c>
       <c r="R86" t="n">
-        <v>6943785</v>
+        <v>6943586</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10190,17 +9841,27 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Inspelad ett flertal gånger I augusti 2025</t>
+          <t>Vid litet surdråg</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10227,10 +9888,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127830118</v>
+        <v>119601996</v>
       </c>
       <c r="B87" t="n">
-        <v>57334</v>
+        <v>79085</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10238,49 +9899,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100063</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Storöravattnet, Storöravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>490736</v>
+        <v>490657</v>
       </c>
       <c r="R87" t="n">
-        <v>6943785</v>
+        <v>6943791</v>
       </c>
       <c r="S87" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10304,17 +9953,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Läte inspelat, mest troligt under förbiflygning</t>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10341,10 +9995,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127830103</v>
+        <v>119562305</v>
       </c>
       <c r="B88" t="n">
-        <v>58115</v>
+        <v>79917</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10352,49 +10006,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103001</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>490736</v>
+        <v>490757</v>
       </c>
       <c r="R88" t="n">
-        <v>6943785</v>
+        <v>6943439</v>
       </c>
       <c r="S88" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10418,12 +10060,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10447,120 +10099,6 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>127830121</v>
-      </c>
-      <c r="B89" t="n">
-        <v>57845</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Stor-Öravattnet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>490736</v>
-      </c>
-      <c r="R89" t="n">
-        <v>6943785</v>
-      </c>
-      <c r="S89" t="n">
-        <v>50</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Hackås</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Inspelad ett flertal gånger I augusti 2025</t>
-        </is>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33056-2024 artfynd.xlsx
+++ b/artfynd/A 33056-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AZ88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119567445</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119604751</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611969</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302751</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119561285</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119560972</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119573937</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611930</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1623,6 +1668,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119564989</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1730,6 +1780,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119566746</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1837,6 +1892,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599421</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119600343</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2051,6 +2116,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602140</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2158,6 +2228,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304206</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2265,6 +2340,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119560369</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2372,6 +2452,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119561375</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2479,6 +2564,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119562658</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2586,6 +2676,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119565707</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2693,6 +2788,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119566845</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2800,6 +2900,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119567943</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2907,6 +3012,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119570334</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3014,6 +3124,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119570901</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3121,6 +3236,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119598830</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3228,6 +3348,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599504</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3335,6 +3460,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119603478</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3442,6 +3572,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302585</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3549,6 +3684,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127305232</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3661,6 +3801,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119565471</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3768,6 +3913,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119565821</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3875,6 +4025,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119566592</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3982,6 +4137,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119567047</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4089,6 +4249,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119598641</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4196,6 +4361,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599288</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4303,6 +4473,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605333</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4404,6 +4579,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611984</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4511,6 +4691,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303436</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4618,6 +4803,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117159903</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4730,6 +4920,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119567682</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4837,6 +5032,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119567978</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4949,6 +5149,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119568892</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5056,6 +5261,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119569970</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5163,6 +5373,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119570068</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5270,6 +5485,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119570160</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5377,6 +5597,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119570243</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5484,6 +5709,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119570777</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5591,6 +5821,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119598920</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5698,6 +5933,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119603962</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5805,6 +6045,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119604081</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5912,6 +6157,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605869</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6013,6 +6263,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611689</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6114,6 +6369,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119612016</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6226,6 +6486,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303834</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6333,6 +6598,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304672</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6440,6 +6710,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127305164</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6547,6 +6822,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119567326</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6654,6 +6934,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304100</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6761,6 +7046,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119567265</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6862,6 +7152,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119612059</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6969,6 +7264,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119568960</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7076,6 +7376,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119603940</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7190,6 +7495,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830118</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7302,6 +7612,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599641</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7412,6 +7727,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119612354</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7528,6 +7848,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119570130</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7640,6 +7965,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605344</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7754,6 +8084,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830123</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7863,6 +8198,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830103</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7977,6 +8317,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830119</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8089,6 +8434,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119562537</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8203,6 +8553,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830121</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8317,6 +8672,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830128</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8433,6 +8793,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119563399</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8549,6 +8914,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119568632</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8665,6 +9035,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119568797</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8781,6 +9156,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119569122</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8897,6 +9277,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119569440</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9013,6 +9398,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119569847</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9123,6 +9513,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611850</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9233,6 +9628,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611864</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9335,6 +9735,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611906</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9437,6 +9842,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611914</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9547,6 +9957,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611950</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9657,6 +10072,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119612090</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9773,6 +10193,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304951</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9885,6 +10310,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304399</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9992,6 +10422,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119601996</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10099,8 +10534,102 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119562305</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>